--- a/research/rasmiy-2026-10-14/banklar_kredit_omonat_rasmiy.xlsx
+++ b/research/rasmiy-2026-10-14/banklar_kredit_omonat_rasmiy.xlsx
@@ -2610,7 +2610,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Istisno: Asakabank sayti mahsulotlarni faqat O'zbekistondan ko'rsatadi, shuning uchun uning foizlari bank.uz va depozit.uz agregatorlaridan olingan (har bir qatorda belgilangan).</t>
+          <t>Istisno: Asakabank sayti mahsulotlarni faqat O'zbekistondan ko'rsatadi, shuning uchun uning foizlari bank.uz agregatoridan olingan (har bir qatorda belgilangan).</t>
         </is>
       </c>
     </row>

--- a/research/rasmiy-2026-10-14/banklar_kredit_omonat_rasmiy.xlsx
+++ b/research/rasmiy-2026-10-14/banklar_kredit_omonat_rasmiy.xlsx
@@ -1643,7 +1643,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Smartbank</t>
+          <t>Openbank</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -1660,7 +1660,7 @@
       <c r="E54" s="3" t="inlineStr"/>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>https://smartbank.uz/useful/faq</t>
+          <t>https://openbank.uz/faq</t>
         </is>
       </c>
     </row>
@@ -20616,7 +20616,7 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>Orient Finans Bank</t>
+          <t>Openbank</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
@@ -20626,31 +20626,23 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit Ikkilamchi bozorga</t>
+          <t>Kredit</t>
         </is>
       </c>
       <c r="E319" s="3" t="n">
-        <v>24.9</v>
+        <v>24.99</v>
       </c>
       <c r="F319" s="3" t="n">
-        <v>24.9</v>
+        <v>25.99</v>
       </c>
       <c r="G319" s="3" t="inlineStr"/>
-      <c r="H319" s="3" t="inlineStr">
-        <is>
-          <t>4 yilgacha</t>
-        </is>
-      </c>
-      <c r="I319" s="3" t="inlineStr">
-        <is>
-          <t>800 mln gacha</t>
-        </is>
-      </c>
+      <c r="H319" s="3" t="inlineStr"/>
+      <c r="I319" s="3" t="inlineStr"/>
       <c r="J319" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -20658,18 +20650,18 @@
       </c>
       <c r="K319" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L319" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M319" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L319" s="3" t="inlineStr"/>
+      <c r="M319" s="3" t="inlineStr">
+        <is>
+          <t>Rasmiy daromadli 24.99%, o'zini band qilganlar 25.99%</t>
+        </is>
+      </c>
       <c r="N319" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/ikkilamchi-bozor-uchun-avtokredit</t>
+          <t>https://openbank.uz/faq</t>
         </is>
       </c>
     </row>
@@ -20691,19 +20683,19 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit Import</t>
+          <t>Avtokredit Ikkilamchi bozorga</t>
         </is>
       </c>
       <c r="E320" s="3" t="n">
-        <v>22.9</v>
+        <v>24.9</v>
       </c>
       <c r="F320" s="3" t="n">
-        <v>22.9</v>
+        <v>24.9</v>
       </c>
       <c r="G320" s="3" t="inlineStr"/>
       <c r="H320" s="3" t="inlineStr">
         <is>
-          <t>5 yilgacha</t>
+          <t>4 yilgacha</t>
         </is>
       </c>
       <c r="I320" s="3" t="inlineStr">
@@ -20729,7 +20721,7 @@
       <c r="M320" s="3" t="inlineStr"/>
       <c r="N320" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/import-avtokredit</t>
+          <t>https://ofb.uz/kreditlar/ikkilamchi-bozor-uchun-avtokredit</t>
         </is>
       </c>
     </row>
@@ -20751,19 +20743,19 @@
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit Foydali</t>
+          <t>Avtokredit Import</t>
         </is>
       </c>
       <c r="E321" s="3" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
       <c r="F321" s="3" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
       <c r="G321" s="3" t="inlineStr"/>
       <c r="H321" s="3" t="inlineStr">
         <is>
-          <t>1 yilgacha</t>
+          <t>5 yilgacha</t>
         </is>
       </c>
       <c r="I321" s="3" t="inlineStr">
@@ -20789,7 +20781,7 @@
       <c r="M321" s="3" t="inlineStr"/>
       <c r="N321" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/avtokredit-foydali</t>
+          <t>https://ofb.uz/kreditlar/import-avtokredit</t>
         </is>
       </c>
     </row>
@@ -20811,19 +20803,19 @@
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Oson avtokredit</t>
+          <t>Avtokredit Foydali</t>
         </is>
       </c>
       <c r="E322" s="3" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F322" s="3" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="G322" s="3" t="inlineStr"/>
       <c r="H322" s="3" t="inlineStr">
         <is>
-          <t>5 yilgacha</t>
+          <t>1 yilgacha</t>
         </is>
       </c>
       <c r="I322" s="3" t="inlineStr">
@@ -20849,7 +20841,7 @@
       <c r="M322" s="3" t="inlineStr"/>
       <c r="N322" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/oson-avtokredit</t>
+          <t>https://ofb.uz/kreditlar/avtokredit-foydali</t>
         </is>
       </c>
     </row>
@@ -20871,21 +20863,19 @@
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>Byudjet tashkilotlari xodimlari uchun</t>
+          <t>Oson avtokredit</t>
         </is>
       </c>
       <c r="E323" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F323" s="3" t="n"/>
-      <c r="G323" s="3" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
+        <v>21.9</v>
+      </c>
+      <c r="F323" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G323" s="3" t="inlineStr"/>
       <c r="H323" s="3" t="inlineStr">
         <is>
-          <t>60 oygacha</t>
+          <t>5 yilgacha</t>
         </is>
       </c>
       <c r="I323" s="3" t="inlineStr">
@@ -20900,18 +20890,18 @@
       </c>
       <c r="K323" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L323" s="3" t="inlineStr"/>
-      <c r="M323" s="3" t="inlineStr">
-        <is>
-          <t>Boshlang'ich badalga qarab pasayadi</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L323" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M323" s="3" t="inlineStr"/>
       <c r="N323" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/byudjet-tashkilotlari-xodimlari-uchun-avtokredit</t>
+          <t>https://ofb.uz/kreditlar/oson-avtokredit</t>
         </is>
       </c>
     </row>
@@ -20933,17 +20923,21 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>BYD Special Plus</t>
+          <t>Byudjet tashkilotlari xodimlari uchun</t>
         </is>
       </c>
       <c r="E324" s="3" t="n">
-        <v>12.5</v>
+        <v>20.9</v>
       </c>
       <c r="F324" s="3" t="n"/>
-      <c r="G324" s="3" t="inlineStr"/>
+      <c r="G324" s="3" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
       <c r="H324" s="3" t="inlineStr">
         <is>
-          <t>36 / 60 oy</t>
+          <t>60 oygacha</t>
         </is>
       </c>
       <c r="I324" s="3" t="inlineStr">
@@ -20964,12 +20958,12 @@
       <c r="L324" s="3" t="inlineStr"/>
       <c r="M324" s="3" t="inlineStr">
         <is>
-          <t>Yangi BYD avtomobillari</t>
+          <t>Boshlang'ich badalga qarab pasayadi</t>
         </is>
       </c>
       <c r="N324" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/byd-special-plus</t>
+          <t>https://ofb.uz/kreditlar/byudjet-tashkilotlari-xodimlari-uchun-avtokredit</t>
         </is>
       </c>
     </row>
@@ -20986,29 +20980,27 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>OFB Start</t>
+          <t>BYD Special Plus</t>
         </is>
       </c>
       <c r="E325" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F325" s="3" t="n">
-        <v>28</v>
-      </c>
+        <v>12.5</v>
+      </c>
+      <c r="F325" s="3" t="n"/>
       <c r="G325" s="3" t="inlineStr"/>
       <c r="H325" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 3 yil</t>
+          <t>36 / 60 oy</t>
         </is>
       </c>
       <c r="I325" s="3" t="inlineStr">
         <is>
-          <t>5.33715 mln – 1 mlrd</t>
+          <t>800 mln gacha</t>
         </is>
       </c>
       <c r="J325" s="3" t="inlineStr">
@@ -21018,18 +21010,18 @@
       </c>
       <c r="K325" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L325" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M325" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L325" s="3" t="inlineStr"/>
+      <c r="M325" s="3" t="inlineStr">
+        <is>
+          <t>Yangi BYD avtomobillari</t>
+        </is>
+      </c>
       <c r="N325" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-start</t>
+          <t>https://ofb.uz/kreditlar/byd-special-plus</t>
         </is>
       </c>
     </row>
@@ -21051,11 +21043,11 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>OFB Ishonchli</t>
+          <t>OFB Start</t>
         </is>
       </c>
       <c r="E326" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F326" s="3" t="n">
         <v>28</v>
@@ -21063,12 +21055,12 @@
       <c r="G326" s="3" t="inlineStr"/>
       <c r="H326" s="3" t="inlineStr">
         <is>
-          <t>2 oy – 2 yil</t>
+          <t>3 oy – 3 yil</t>
         </is>
       </c>
       <c r="I326" s="3" t="inlineStr">
         <is>
-          <t>18.0539 mln – 2 mlrd</t>
+          <t>5.33715 mln – 1 mlrd</t>
         </is>
       </c>
       <c r="J326" s="3" t="inlineStr">
@@ -21089,7 +21081,7 @@
       <c r="M326" s="3" t="inlineStr"/>
       <c r="N326" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-ishonchli</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-start</t>
         </is>
       </c>
     </row>
@@ -21111,14 +21103,14 @@
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>OFB Cash</t>
+          <t>OFB Ishonchli</t>
         </is>
       </c>
       <c r="E327" s="3" t="n">
         <v>26</v>
       </c>
       <c r="F327" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G327" s="3" t="inlineStr"/>
       <c r="H327" s="3" t="inlineStr">
@@ -21128,7 +21120,7 @@
       </c>
       <c r="I327" s="3" t="inlineStr">
         <is>
-          <t>17.9531 mln – 1 mlrd</t>
+          <t>18.0539 mln – 2 mlrd</t>
         </is>
       </c>
       <c r="J327" s="3" t="inlineStr">
@@ -21149,7 +21141,7 @@
       <c r="M327" s="3" t="inlineStr"/>
       <c r="N327" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-cash</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-ishonchli</t>
         </is>
       </c>
     </row>
@@ -21171,11 +21163,11 @@
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>OFB Kapital</t>
+          <t>OFB Cash</t>
         </is>
       </c>
       <c r="E328" s="3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F328" s="3" t="n">
         <v>26</v>
@@ -21183,12 +21175,12 @@
       <c r="G328" s="3" t="inlineStr"/>
       <c r="H328" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 3 yil</t>
+          <t>2 oy – 2 yil</t>
         </is>
       </c>
       <c r="I328" s="3" t="inlineStr">
         <is>
-          <t>9.55301 mln – 3 mlrd</t>
+          <t>17.9531 mln – 1 mlrd</t>
         </is>
       </c>
       <c r="J328" s="3" t="inlineStr">
@@ -21209,7 +21201,7 @@
       <c r="M328" s="3" t="inlineStr"/>
       <c r="N328" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-kapital</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-cash</t>
         </is>
       </c>
     </row>
@@ -21231,14 +21223,14 @@
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
-          <t>OFB Garant</t>
+          <t>OFB Kapital</t>
         </is>
       </c>
       <c r="E329" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F329" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G329" s="3" t="inlineStr"/>
       <c r="H329" s="3" t="inlineStr">
@@ -21248,7 +21240,7 @@
       </c>
       <c r="I329" s="3" t="inlineStr">
         <is>
-          <t>93.75 ming – 5 mln</t>
+          <t>9.55301 mln – 3 mlrd</t>
         </is>
       </c>
       <c r="J329" s="3" t="inlineStr">
@@ -21269,7 +21261,7 @@
       <c r="M329" s="3" t="inlineStr"/>
       <c r="N329" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-garant</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-kapital</t>
         </is>
       </c>
     </row>
@@ -21291,24 +21283,24 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>OFB Kelajak</t>
+          <t>OFB Garant</t>
         </is>
       </c>
       <c r="E330" s="3" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="F330" s="3" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="G330" s="3" t="inlineStr"/>
       <c r="H330" s="3" t="inlineStr">
         <is>
-          <t>2 oy – 2 yil</t>
+          <t>3 oy – 3 yil</t>
         </is>
       </c>
       <c r="I330" s="3" t="inlineStr">
         <is>
-          <t>259.193 ming – 1.64891 mln</t>
+          <t>93.75 ming – 5 mln</t>
         </is>
       </c>
       <c r="J330" s="3" t="inlineStr">
@@ -21329,7 +21321,7 @@
       <c r="M330" s="3" t="inlineStr"/>
       <c r="N330" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-kelajak</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-garant</t>
         </is>
       </c>
     </row>
@@ -21346,29 +21338,29 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>Foydali ipoteka</t>
+          <t>OFB Kelajak</t>
         </is>
       </c>
       <c r="E331" s="3" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="F331" s="3" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="G331" s="3" t="inlineStr"/>
       <c r="H331" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 20 yil</t>
+          <t>2 oy – 2 yil</t>
         </is>
       </c>
       <c r="I331" s="3" t="inlineStr">
         <is>
-          <t>7.82892 mln – 1.06 mlrd</t>
+          <t>259.193 ming – 1.64891 mln</t>
         </is>
       </c>
       <c r="J331" s="3" t="inlineStr">
@@ -21389,7 +21381,7 @@
       <c r="M331" s="3" t="inlineStr"/>
       <c r="N331" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/foydali-ipoteka</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-kelajak</t>
         </is>
       </c>
     </row>
@@ -21411,24 +21403,24 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Uy-joy ta'miri uchun ipoteka</t>
+          <t>Foydali ipoteka</t>
         </is>
       </c>
       <c r="E332" s="3" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F332" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G332" s="3" t="inlineStr"/>
       <c r="H332" s="3" t="inlineStr">
         <is>
-          <t>10 yilgacha</t>
+          <t>6 oy – 20 yil</t>
         </is>
       </c>
       <c r="I332" s="3" t="inlineStr">
         <is>
-          <t>400 mln gacha</t>
+          <t>7.82892 mln – 1.06 mlrd</t>
         </is>
       </c>
       <c r="J332" s="3" t="inlineStr">
@@ -21438,14 +21430,18 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L332" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L332" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M332" s="3" t="inlineStr"/>
       <c r="N332" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/tamirlash-uchun-ipoteka-krediti</t>
+          <t>https://ofb.uz/kreditlar/foydali-ipoteka</t>
         </is>
       </c>
     </row>
@@ -21467,7 +21463,7 @@
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>Ta’mirlash uchun ipoteka krediti</t>
+          <t>Uy-joy ta'miri uchun ipoteka</t>
         </is>
       </c>
       <c r="E333" s="3" t="n">
@@ -21494,14 +21490,10 @@
       </c>
       <c r="K333" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L333" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L333" s="3" t="inlineStr"/>
       <c r="M333" s="3" t="inlineStr"/>
       <c r="N333" s="6" t="inlineStr">
         <is>
@@ -21527,7 +21519,7 @@
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Yashil ipoteka</t>
+          <t>Ta’mirlash uchun ipoteka krediti</t>
         </is>
       </c>
       <c r="E334" s="3" t="n">
@@ -21539,12 +21531,12 @@
       <c r="G334" s="3" t="inlineStr"/>
       <c r="H334" s="3" t="inlineStr">
         <is>
-          <t>7 yilgacha</t>
+          <t>10 yilgacha</t>
         </is>
       </c>
       <c r="I334" s="3" t="inlineStr">
         <is>
-          <t>350 mln gacha</t>
+          <t>400 mln gacha</t>
         </is>
       </c>
       <c r="J334" s="3" t="inlineStr">
@@ -21565,7 +21557,7 @@
       <c r="M334" s="3" t="inlineStr"/>
       <c r="N334" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/yashil-ipoteka</t>
+          <t>https://ofb.uz/kreditlar/tamirlash-uchun-ipoteka-krediti</t>
         </is>
       </c>
     </row>
@@ -21587,24 +21579,24 @@
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>Navro‘z ipoteka krediti</t>
+          <t>Yashil ipoteka</t>
         </is>
       </c>
       <c r="E335" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F335" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G335" s="3" t="inlineStr"/>
       <c r="H335" s="3" t="inlineStr">
         <is>
-          <t>20 yilgacha</t>
+          <t>7 yilgacha</t>
         </is>
       </c>
       <c r="I335" s="3" t="inlineStr">
         <is>
-          <t>1.06 mlrd gacha</t>
+          <t>350 mln gacha</t>
         </is>
       </c>
       <c r="J335" s="3" t="inlineStr">
@@ -21625,7 +21617,7 @@
       <c r="M335" s="3" t="inlineStr"/>
       <c r="N335" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/navroz-ipoteka-krediti</t>
+          <t>https://ofb.uz/kreditlar/yashil-ipoteka</t>
         </is>
       </c>
     </row>
@@ -21647,14 +21639,14 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Birlamchi bozor uchun ipoteka 2.0</t>
+          <t>Navro‘z ipoteka krediti</t>
         </is>
       </c>
       <c r="E336" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F336" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G336" s="3" t="inlineStr"/>
       <c r="H336" s="3" t="inlineStr">
@@ -21664,7 +21656,7 @@
       </c>
       <c r="I336" s="3" t="inlineStr">
         <is>
-          <t>800 mln gacha</t>
+          <t>1.06 mlrd gacha</t>
         </is>
       </c>
       <c r="J336" s="3" t="inlineStr">
@@ -21685,7 +21677,7 @@
       <c r="M336" s="3" t="inlineStr"/>
       <c r="N336" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/birlamchi-bozor-uchun-2-0</t>
+          <t>https://ofb.uz/kreditlar/navroz-ipoteka-krediti</t>
         </is>
       </c>
     </row>
@@ -21707,24 +21699,24 @@
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka O‘qituvchi</t>
+          <t>Birlamchi bozor uchun ipoteka 2.0</t>
         </is>
       </c>
       <c r="E337" s="3" t="n">
-        <v>16.7</v>
+        <v>19</v>
       </c>
       <c r="F337" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G337" s="3" t="inlineStr"/>
       <c r="H337" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 20 yil</t>
+          <t>20 yilgacha</t>
         </is>
       </c>
       <c r="I337" s="3" t="inlineStr">
         <is>
-          <t>8.26814 mln – 496.088 mln</t>
+          <t>800 mln gacha</t>
         </is>
       </c>
       <c r="J337" s="3" t="inlineStr">
@@ -21745,7 +21737,7 @@
       <c r="M337" s="3" t="inlineStr"/>
       <c r="N337" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/ipoteka-oqituvchi</t>
+          <t>https://ofb.uz/kreditlar/birlamchi-bozor-uchun-2-0</t>
         </is>
       </c>
     </row>
@@ -21767,14 +21759,14 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Oilaviy ipoteka</t>
+          <t>Ipoteka O‘qituvchi</t>
         </is>
       </c>
       <c r="E338" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="F338" s="3" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="G338" s="3" t="inlineStr"/>
       <c r="H338" s="3" t="inlineStr">
@@ -21805,7 +21797,7 @@
       <c r="M338" s="3" t="inlineStr"/>
       <c r="N338" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/oilaviy-ipoteka</t>
+          <t>https://ofb.uz/kreditlar/ipoteka-oqituvchi</t>
         </is>
       </c>
     </row>
@@ -21822,29 +21814,29 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>Corporate Plus</t>
+          <t>Oilaviy ipoteka</t>
         </is>
       </c>
       <c r="E339" s="3" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="F339" s="3" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="G339" s="3" t="inlineStr"/>
       <c r="H339" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>6 oy – 20 yil</t>
         </is>
       </c>
       <c r="I339" s="3" t="inlineStr">
         <is>
-          <t>100 mln gacha</t>
+          <t>8.26814 mln – 496.088 mln</t>
         </is>
       </c>
       <c r="J339" s="3" t="inlineStr">
@@ -21865,7 +21857,7 @@
       <c r="M339" s="3" t="inlineStr"/>
       <c r="N339" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/corporate-plus</t>
+          <t>https://ofb.uz/kreditlar/oilaviy-ipoteka</t>
         </is>
       </c>
     </row>
@@ -21887,20 +21879,24 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Qulay qayta moliyalashtirish</t>
+          <t>Corporate Plus</t>
         </is>
       </c>
       <c r="E340" s="3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F340" s="3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G340" s="3" t="inlineStr"/>
-      <c r="H340" s="3" t="inlineStr"/>
+      <c r="H340" s="3" t="inlineStr">
+        <is>
+          <t>3 yilgacha</t>
+        </is>
+      </c>
       <c r="I340" s="3" t="inlineStr">
         <is>
-          <t>1.72392 mln – 1 mlrd</t>
+          <t>100 mln gacha</t>
         </is>
       </c>
       <c r="J340" s="3" t="inlineStr">
@@ -21921,7 +21917,7 @@
       <c r="M340" s="3" t="inlineStr"/>
       <c r="N340" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/qulay-qayta-moliyalashtirish</t>
+          <t>https://ofb.uz/kreditlar/corporate-plus</t>
         </is>
       </c>
     </row>
@@ -21943,20 +21939,20 @@
       </c>
       <c r="D341" s="3" t="inlineStr">
         <is>
-          <t>Bashkent</t>
+          <t>Qulay qayta moliyalashtirish</t>
         </is>
       </c>
       <c r="E341" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G341" s="3" t="inlineStr"/>
       <c r="H341" s="3" t="inlineStr"/>
       <c r="I341" s="3" t="inlineStr">
         <is>
-          <t>1.06 mlrd gacha</t>
+          <t>1.72392 mln – 1 mlrd</t>
         </is>
       </c>
       <c r="J341" s="3" t="inlineStr">
@@ -21977,7 +21973,7 @@
       <c r="M341" s="3" t="inlineStr"/>
       <c r="N341" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/bashkent</t>
+          <t>https://ofb.uz/kreditlar/qulay-qayta-moliyalashtirish</t>
         </is>
       </c>
     </row>
@@ -21994,29 +21990,25 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>Kredit karta</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Biznes Karta</t>
+          <t>Bashkent</t>
         </is>
       </c>
       <c r="E342" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G342" s="3" t="inlineStr"/>
-      <c r="H342" s="3" t="inlineStr">
-        <is>
-          <t>2 oy – 1 yil</t>
-        </is>
-      </c>
+      <c r="H342" s="3" t="inlineStr"/>
       <c r="I342" s="3" t="inlineStr">
         <is>
-          <t>17.9028 mln – 500 mln</t>
+          <t>1.06 mlrd gacha</t>
         </is>
       </c>
       <c r="J342" s="3" t="inlineStr">
@@ -22037,7 +22029,7 @@
       <c r="M342" s="3" t="inlineStr"/>
       <c r="N342" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/biznes-karta</t>
+          <t>https://ofb.uz/kreditlar/bashkent</t>
         </is>
       </c>
     </row>
@@ -22059,24 +22051,24 @@
       </c>
       <c r="D343" s="3" t="inlineStr">
         <is>
-          <t>Biznes Overdraft</t>
+          <t>Biznes Karta</t>
         </is>
       </c>
       <c r="E343" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F343" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G343" s="3" t="inlineStr"/>
       <c r="H343" s="3" t="inlineStr">
         <is>
-          <t>2 oy – 18 oy</t>
+          <t>2 oy – 1 yil</t>
         </is>
       </c>
       <c r="I343" s="3" t="inlineStr">
         <is>
-          <t>17.9028 mln – 1.5 mlrd</t>
+          <t>17.9028 mln – 500 mln</t>
         </is>
       </c>
       <c r="J343" s="3" t="inlineStr">
@@ -22097,7 +22089,7 @@
       <c r="M343" s="3" t="inlineStr"/>
       <c r="N343" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/biznes-overdraft</t>
+          <t>https://ofb.uz/biznes/kreditlar/biznes-karta</t>
         </is>
       </c>
     </row>
@@ -22119,24 +22111,24 @@
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Overdraft</t>
+          <t>Biznes Overdraft</t>
         </is>
       </c>
       <c r="E344" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F344" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G344" s="3" t="inlineStr"/>
       <c r="H344" s="3" t="inlineStr">
         <is>
-          <t>2 yilgacha</t>
+          <t>2 oy – 18 oy</t>
         </is>
       </c>
       <c r="I344" s="3" t="inlineStr">
         <is>
-          <t>50 mln gacha</t>
+          <t>17.9028 mln – 1.5 mlrd</t>
         </is>
       </c>
       <c r="J344" s="3" t="inlineStr">
@@ -22157,7 +22149,7 @@
       <c r="M344" s="3" t="inlineStr"/>
       <c r="N344" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/overdraft</t>
+          <t>https://ofb.uz/biznes/kreditlar/biznes-overdraft</t>
         </is>
       </c>
     </row>
@@ -22174,24 +22166,24 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Kredit karta</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
         <is>
-          <t>Onlayn mikroqarz (ilova)</t>
+          <t>Overdraft</t>
         </is>
       </c>
       <c r="E345" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F345" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G345" s="3" t="inlineStr"/>
       <c r="H345" s="3" t="inlineStr">
         <is>
-          <t>24 oygacha</t>
+          <t>2 yilgacha</t>
         </is>
       </c>
       <c r="I345" s="3" t="inlineStr">
@@ -22206,14 +22198,18 @@
       </c>
       <c r="K345" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L345" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L345" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M345" s="3" t="inlineStr"/>
       <c r="N345" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/en/credits/online-microloan</t>
+          <t>https://ofb.uz/kreditlar/overdraft</t>
         </is>
       </c>
     </row>
@@ -22235,7 +22231,7 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Onlayn mikroqarz</t>
+          <t>Onlayn mikroqarz (ilova)</t>
         </is>
       </c>
       <c r="E346" s="3" t="n">
@@ -22245,7 +22241,11 @@
         <v>30</v>
       </c>
       <c r="G346" s="3" t="inlineStr"/>
-      <c r="H346" s="3" t="inlineStr"/>
+      <c r="H346" s="3" t="inlineStr">
+        <is>
+          <t>24 oygacha</t>
+        </is>
+      </c>
       <c r="I346" s="3" t="inlineStr">
         <is>
           <t>50 mln gacha</t>
@@ -22258,18 +22258,14 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L346" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/onlayn-mikroqarz</t>
+          <t>https://ofb.uz/en/credits/online-microloan</t>
         </is>
       </c>
     </row>
@@ -22291,24 +22287,20 @@
       </c>
       <c r="D347" s="3" t="inlineStr">
         <is>
-          <t>Kichik biznesga qadam</t>
+          <t>Onlayn mikroqarz</t>
         </is>
       </c>
       <c r="E347" s="3" t="n">
-        <v>27.4</v>
+        <v>30</v>
       </c>
       <c r="F347" s="3" t="n">
-        <v>27.4</v>
+        <v>30</v>
       </c>
       <c r="G347" s="3" t="inlineStr"/>
-      <c r="H347" s="3" t="inlineStr">
-        <is>
-          <t>2 yilgacha</t>
-        </is>
-      </c>
+      <c r="H347" s="3" t="inlineStr"/>
       <c r="I347" s="3" t="inlineStr">
         <is>
-          <t>5 mln gacha</t>
+          <t>50 mln gacha</t>
         </is>
       </c>
       <c r="J347" s="3" t="inlineStr">
@@ -22329,7 +22321,7 @@
       <c r="M347" s="3" t="inlineStr"/>
       <c r="N347" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/kichik-biznesga-qadam-mikrozaymi</t>
+          <t>https://ofb.uz/kreditlar/onlayn-mikroqarz</t>
         </is>
       </c>
     </row>
@@ -22351,24 +22343,24 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>O‘simlikchilik</t>
+          <t>Kichik biznesga qadam</t>
         </is>
       </c>
       <c r="E348" s="3" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="F348" s="3" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="G348" s="3" t="inlineStr"/>
       <c r="H348" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>2 yilgacha</t>
         </is>
       </c>
       <c r="I348" s="3" t="inlineStr">
         <is>
-          <t>30 mln gacha</t>
+          <t>5 mln gacha</t>
         </is>
       </c>
       <c r="J348" s="3" t="inlineStr">
@@ -22389,7 +22381,7 @@
       <c r="M348" s="3" t="inlineStr"/>
       <c r="N348" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/osimlikchilik-mikrozaymi</t>
+          <t>https://ofb.uz/kreditlar/kichik-biznesga-qadam-mikrozaymi</t>
         </is>
       </c>
     </row>
@@ -22411,7 +22403,7 @@
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>Bog‘bon</t>
+          <t>O‘simlikchilik</t>
         </is>
       </c>
       <c r="E349" s="3" t="n">
@@ -22428,7 +22420,7 @@
       </c>
       <c r="I349" s="3" t="inlineStr">
         <is>
-          <t>20 mln gacha</t>
+          <t>30 mln gacha</t>
         </is>
       </c>
       <c r="J349" s="3" t="inlineStr">
@@ -22449,7 +22441,7 @@
       <c r="M349" s="3" t="inlineStr"/>
       <c r="N349" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/bogbon-mikrozaymi</t>
+          <t>https://ofb.uz/kreditlar/osimlikchilik-mikrozaymi</t>
         </is>
       </c>
     </row>
@@ -22471,28 +22463,24 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz Ichki turizm</t>
+          <t>Bog‘bon</t>
         </is>
       </c>
       <c r="E350" s="3" t="n">
-        <v>26</v>
+        <v>26.9</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="G350" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+        <v>26.9</v>
+      </c>
+      <c r="G350" s="3" t="inlineStr"/>
       <c r="H350" s="3" t="inlineStr">
         <is>
-          <t>12 oygacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I350" s="3" t="inlineStr">
         <is>
-          <t>15 mln gacha</t>
+          <t>20 mln gacha</t>
         </is>
       </c>
       <c r="J350" s="3" t="inlineStr">
@@ -22502,14 +22490,18 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L350" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L350" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/mikroqarz-ichki-turizm</t>
+          <t>https://ofb.uz/kreditlar/bogbon-mikrozaymi</t>
         </is>
       </c>
     </row>
@@ -22531,19 +22523,23 @@
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>Start Up</t>
+          <t>Mikroqarz Ichki turizm</t>
         </is>
       </c>
       <c r="E351" s="3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="F351" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G351" s="3" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="G351" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="H351" s="3" t="inlineStr">
         <is>
-          <t>1 yilgacha</t>
+          <t>12 oygacha</t>
         </is>
       </c>
       <c r="I351" s="3" t="inlineStr">
@@ -22558,18 +22554,14 @@
       </c>
       <c r="K351" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L351" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L351" s="3" t="inlineStr"/>
       <c r="M351" s="3" t="inlineStr"/>
       <c r="N351" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/start-up-mikrozaymi</t>
+          <t>https://ofb.uz/kreditlar/mikroqarz-ichki-turizm</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22583,7 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>Oilaviy biznes</t>
+          <t>Start Up</t>
         </is>
       </c>
       <c r="E352" s="3" t="n">
@@ -22603,12 +22595,12 @@
       <c r="G352" s="3" t="inlineStr"/>
       <c r="H352" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>1 yilgacha</t>
         </is>
       </c>
       <c r="I352" s="3" t="inlineStr">
         <is>
-          <t>25 mln gacha</t>
+          <t>15 mln gacha</t>
         </is>
       </c>
       <c r="J352" s="3" t="inlineStr">
@@ -22629,7 +22621,7 @@
       <c r="M352" s="3" t="inlineStr"/>
       <c r="N352" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/oilaviy-biznes-mikrozaymi</t>
+          <t>https://ofb.uz/kreditlar/start-up-mikrozaymi</t>
         </is>
       </c>
     </row>
@@ -22651,14 +22643,14 @@
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>Ishonch</t>
+          <t>Oilaviy biznes</t>
         </is>
       </c>
       <c r="E353" s="3" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="F353" s="3" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="G353" s="3" t="inlineStr"/>
       <c r="H353" s="3" t="inlineStr">
@@ -22668,7 +22660,7 @@
       </c>
       <c r="I353" s="3" t="inlineStr">
         <is>
-          <t>100 mln gacha</t>
+          <t>25 mln gacha</t>
         </is>
       </c>
       <c r="J353" s="3" t="inlineStr">
@@ -22689,7 +22681,7 @@
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/ishonch-mikroqarz</t>
+          <t>https://ofb.uz/kreditlar/oilaviy-biznes-mikrozaymi</t>
         </is>
       </c>
     </row>
@@ -22711,24 +22703,24 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Green mikroqarz</t>
+          <t>Ishonch</t>
         </is>
       </c>
       <c r="E354" s="3" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="F354" s="3" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="G354" s="3" t="inlineStr"/>
       <c r="H354" s="3" t="inlineStr">
         <is>
-          <t>36 oygacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I354" s="3" t="inlineStr">
         <is>
-          <t>5–50 mln</t>
+          <t>100 mln gacha</t>
         </is>
       </c>
       <c r="J354" s="3" t="inlineStr">
@@ -22738,14 +22730,18 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L354" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L354" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M354" s="3" t="inlineStr"/>
       <c r="N354" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/green-mikroqarz</t>
+          <t>https://ofb.uz/kreditlar/ishonch-mikroqarz</t>
         </is>
       </c>
     </row>
@@ -22762,29 +22758,29 @@
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>Ta'lim</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>Ta’lim uchun</t>
+          <t>Green mikroqarz</t>
         </is>
       </c>
       <c r="E355" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F355" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G355" s="3" t="inlineStr"/>
       <c r="H355" s="3" t="inlineStr">
         <is>
-          <t>4 yilgacha</t>
+          <t>36 oygacha</t>
         </is>
       </c>
       <c r="I355" s="3" t="inlineStr">
         <is>
-          <t>250 mln gacha</t>
+          <t>5–50 mln</t>
         </is>
       </c>
       <c r="J355" s="3" t="inlineStr">
@@ -22794,18 +22790,14 @@
       </c>
       <c r="K355" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L355" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L355" s="3" t="inlineStr"/>
       <c r="M355" s="3" t="inlineStr"/>
       <c r="N355" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/talim-uchun-istemol-krediti</t>
+          <t>https://ofb.uz/kreditlar/green-mikroqarz</t>
         </is>
       </c>
     </row>
@@ -22817,36 +22809,34 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Ta'lim</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>OFB Express (aylanma mablag')</t>
+          <t>Ta’lim uchun</t>
         </is>
       </c>
       <c r="E356" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F356" s="3" t="n"/>
-      <c r="G356" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F356" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G356" s="3" t="inlineStr"/>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t>24 oygacha</t>
+          <t>4 yilgacha</t>
         </is>
       </c>
       <c r="I356" s="3" t="inlineStr">
         <is>
-          <t>1 mlrd gacha</t>
+          <t>250 mln gacha</t>
         </is>
       </c>
       <c r="J356" s="3" t="inlineStr">
@@ -22856,49 +22846,59 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L356" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L356" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M356" s="3" t="inlineStr"/>
       <c r="N356" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-express</t>
+          <t>https://ofb.uz/kreditlar/talim-uchun-istemol-krediti</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
-          <t>Poytaxt bank</t>
+          <t>Orient Finans Bank</t>
         </is>
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
         <is>
-          <t>"Milliy" avtokredit</t>
+          <t>OFB Express (aylanma mablag')</t>
         </is>
       </c>
       <c r="E357" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F357" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="G357" s="3" t="inlineStr"/>
-      <c r="H357" s="3" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="F357" s="3" t="n"/>
+      <c r="G357" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H357" s="3" t="inlineStr">
+        <is>
+          <t>24 oygacha</t>
+        </is>
+      </c>
       <c r="I357" s="3" t="inlineStr">
         <is>
-          <t>100 mln – 300 mln</t>
+          <t>1 mlrd gacha</t>
         </is>
       </c>
       <c r="J357" s="3" t="inlineStr">
@@ -22908,18 +22908,14 @@
       </c>
       <c r="K357" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L357" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L357" s="3" t="inlineStr"/>
       <c r="M357" s="3" t="inlineStr"/>
       <c r="N357" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/milliy-avtokredit/</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-express</t>
         </is>
       </c>
     </row>
@@ -22941,7 +22937,7 @@
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>"Mini Truck Avto" krediti</t>
+          <t>"Milliy" avtokredit</t>
         </is>
       </c>
       <c r="E358" s="3" t="n">
@@ -22954,7 +22950,7 @@
       <c r="H358" s="3" t="inlineStr"/>
       <c r="I358" s="3" t="inlineStr">
         <is>
-          <t>1 mln – 450 mln</t>
+          <t>100 mln – 300 mln</t>
         </is>
       </c>
       <c r="J358" s="3" t="inlineStr">
@@ -22975,7 +22971,7 @@
       <c r="M358" s="3" t="inlineStr"/>
       <c r="N358" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/mini-truck-avto-krediti/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/milliy-avtokredit/</t>
         </is>
       </c>
     </row>
@@ -22997,22 +22993,22 @@
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>BYD / UzAuto / Hyundai</t>
+          <t>"Mini Truck Avto" krediti</t>
         </is>
       </c>
       <c r="E359" s="3" t="n">
-        <v>24.9</v>
+        <v>20</v>
       </c>
       <c r="F359" s="3" t="n">
-        <v>26.9</v>
+        <v>28</v>
       </c>
       <c r="G359" s="3" t="inlineStr"/>
-      <c r="H359" s="3" t="inlineStr">
-        <is>
-          <t>48 oy</t>
-        </is>
-      </c>
-      <c r="I359" s="3" t="inlineStr"/>
+      <c r="H359" s="3" t="inlineStr"/>
+      <c r="I359" s="3" t="inlineStr">
+        <is>
+          <t>1 mln – 450 mln</t>
+        </is>
+      </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23020,18 +23016,18 @@
       </c>
       <c r="K359" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L359" s="3" t="inlineStr"/>
-      <c r="M359" s="3" t="inlineStr">
-        <is>
-          <t>Ayrim Chevrolet modellari uchun 0%, 60 oygacha</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L359" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M359" s="3" t="inlineStr"/>
       <c r="N359" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/mini-truck-avto-krediti/</t>
         </is>
       </c>
     </row>
@@ -23053,19 +23049,19 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>"Komfort AVTO" avtok... YANGI</t>
+          <t>BYD / UzAuto / Hyundai</t>
         </is>
       </c>
       <c r="E360" s="3" t="n">
-        <v>20</v>
+        <v>24.9</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>24</v>
+        <v>26.9</v>
       </c>
       <c r="G360" s="3" t="inlineStr"/>
       <c r="H360" s="3" t="inlineStr">
         <is>
-          <t>5 yilgacha</t>
+          <t>48 oy</t>
         </is>
       </c>
       <c r="I360" s="3" t="inlineStr"/>
@@ -23076,18 +23072,18 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L360" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M360" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L360" s="3" t="inlineStr"/>
+      <c r="M360" s="3" t="inlineStr">
+        <is>
+          <t>Ayrim Chevrolet modellari uchun 0%, 60 oygacha</t>
+        </is>
+      </c>
       <c r="N360" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/komfort-avto-avtokrediti/</t>
+          <t>https://poytaxtbank.uz/uz/private/</t>
         </is>
       </c>
     </row>
@@ -23104,27 +23100,27 @@
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
         <is>
-          <t>"Biznesga birinchi qadam" krediti</t>
+          <t>"Komfort AVTO" avtok... YANGI</t>
         </is>
       </c>
       <c r="E361" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F361" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G361" s="3" t="inlineStr"/>
-      <c r="H361" s="3" t="inlineStr"/>
-      <c r="I361" s="3" t="inlineStr">
-        <is>
-          <t>18 ming – 15 mln</t>
-        </is>
-      </c>
+      <c r="H361" s="3" t="inlineStr">
+        <is>
+          <t>5 yilgacha</t>
+        </is>
+      </c>
+      <c r="I361" s="3" t="inlineStr"/>
       <c r="J361" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23143,7 +23139,7 @@
       <c r="M361" s="3" t="inlineStr"/>
       <c r="N361" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/first-step-to-business/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/komfort-avto-avtokrediti/</t>
         </is>
       </c>
     </row>
@@ -23165,7 +23161,7 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>"Biznesga ikkinchi qadam" krediti</t>
+          <t>"Biznesga birinchi qadam" krediti</t>
         </is>
       </c>
       <c r="E362" s="3" t="n">
@@ -23178,7 +23174,7 @@
       <c r="H362" s="3" t="inlineStr"/>
       <c r="I362" s="3" t="inlineStr">
         <is>
-          <t>42 ming – 17 mln</t>
+          <t>18 ming – 15 mln</t>
         </is>
       </c>
       <c r="J362" s="3" t="inlineStr">
@@ -23199,7 +23195,7 @@
       <c r="M362" s="3" t="inlineStr"/>
       <c r="N362" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/second-step-to-business/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/first-step-to-business/</t>
         </is>
       </c>
     </row>
@@ -23216,27 +23212,27 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>Maskan</t>
+          <t>"Biznesga ikkinchi qadam" krediti</t>
         </is>
       </c>
       <c r="E363" s="3" t="n">
-        <v>27.99</v>
+        <v>20</v>
       </c>
       <c r="F363" s="3" t="n">
-        <v>31.99</v>
+        <v>28</v>
       </c>
       <c r="G363" s="3" t="inlineStr"/>
-      <c r="H363" s="3" t="inlineStr">
-        <is>
-          <t>5–10 yil</t>
-        </is>
-      </c>
-      <c r="I363" s="3" t="inlineStr"/>
+      <c r="H363" s="3" t="inlineStr"/>
+      <c r="I363" s="3" t="inlineStr">
+        <is>
+          <t>42 ming – 17 mln</t>
+        </is>
+      </c>
       <c r="J363" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23244,18 +23240,18 @@
       </c>
       <c r="K363" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L363" s="3" t="inlineStr"/>
-      <c r="M363" s="3" t="inlineStr">
-        <is>
-          <t>Boshlang'ich badal 25%</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L363" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M363" s="3" t="inlineStr"/>
       <c r="N363" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/mortgage-loan</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/second-step-to-business/</t>
         </is>
       </c>
     </row>
@@ -23277,19 +23273,19 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>«Tayyor Uy» ipoteka krediti YANGI</t>
+          <t>Maskan</t>
         </is>
       </c>
       <c r="E364" s="3" t="n">
-        <v>22.5</v>
+        <v>27.99</v>
       </c>
       <c r="F364" s="3" t="n">
-        <v>24.5</v>
+        <v>31.99</v>
       </c>
       <c r="G364" s="3" t="inlineStr"/>
       <c r="H364" s="3" t="inlineStr">
         <is>
-          <t>20 yilgacha</t>
+          <t>5–10 yil</t>
         </is>
       </c>
       <c r="I364" s="3" t="inlineStr"/>
@@ -23300,18 +23296,18 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L364" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M364" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L364" s="3" t="inlineStr"/>
+      <c r="M364" s="3" t="inlineStr">
+        <is>
+          <t>Boshlang'ich badal 25%</t>
+        </is>
+      </c>
       <c r="N364" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/tayyor-uy-ipoteka-krediti/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/mortgage-loan</t>
         </is>
       </c>
     </row>
@@ -23328,24 +23324,24 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol krediti</t>
+          <t>«Tayyor Uy» ipoteka krediti YANGI</t>
         </is>
       </c>
       <c r="E365" s="3" t="n">
-        <v>28</v>
+        <v>22.5</v>
       </c>
       <c r="F365" s="3" t="n">
-        <v>30</v>
+        <v>24.5</v>
       </c>
       <c r="G365" s="3" t="inlineStr"/>
       <c r="H365" s="3" t="inlineStr">
         <is>
-          <t>12–36 oy</t>
+          <t>20 yilgacha</t>
         </is>
       </c>
       <c r="I365" s="3" t="inlineStr"/>
@@ -23356,18 +23352,18 @@
       </c>
       <c r="K365" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L365" s="3" t="inlineStr"/>
-      <c r="M365" s="3" t="inlineStr">
-        <is>
-          <t>'Sayohat' krediti: 28%, 12 oy</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L365" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M365" s="3" t="inlineStr"/>
       <c r="N365" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/tayyor-uy-ipoteka-krediti/</t>
         </is>
       </c>
     </row>
@@ -23389,22 +23385,22 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>Mahalla loyihasi krediti</t>
+          <t>Iste'mol krediti</t>
         </is>
       </c>
       <c r="E366" s="3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F366" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G366" s="3" t="inlineStr"/>
-      <c r="H366" s="3" t="inlineStr"/>
-      <c r="I366" s="3" t="inlineStr">
-        <is>
-          <t>18 ming – 30 mln</t>
-        </is>
-      </c>
+      <c r="H366" s="3" t="inlineStr">
+        <is>
+          <t>12–36 oy</t>
+        </is>
+      </c>
+      <c r="I366" s="3" t="inlineStr"/>
       <c r="J366" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23412,18 +23408,18 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L366" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M366" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L366" s="3" t="inlineStr"/>
+      <c r="M366" s="3" t="inlineStr">
+        <is>
+          <t>'Sayohat' krediti: 28%, 12 oy</t>
+        </is>
+      </c>
       <c r="N366" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/mahalla-loyihasi-krediti/</t>
+          <t>https://poytaxtbank.uz/uz/private/</t>
         </is>
       </c>
     </row>
@@ -23440,29 +23436,25 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Mahalla loyihasi krediti</t>
         </is>
       </c>
       <c r="E367" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F367" s="3" t="n">
         <v>28</v>
       </c>
       <c r="G367" s="3" t="inlineStr"/>
-      <c r="H367" s="3" t="inlineStr">
-        <is>
-          <t>36 oygacha</t>
-        </is>
-      </c>
+      <c r="H367" s="3" t="inlineStr"/>
       <c r="I367" s="3" t="inlineStr">
         <is>
-          <t>100 mln gacha</t>
+          <t>18 ming – 30 mln</t>
         </is>
       </c>
       <c r="J367" s="3" t="inlineStr">
@@ -23472,18 +23464,18 @@
       </c>
       <c r="K367" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L367" s="3" t="inlineStr"/>
-      <c r="M367" s="3" t="inlineStr">
-        <is>
-          <t>Boshlang'ich badal yo'q</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L367" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M367" s="3" t="inlineStr"/>
       <c r="N367" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/microloan/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/mahalla-loyihasi-krediti/</t>
         </is>
       </c>
     </row>
@@ -23505,7 +23497,7 @@
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz KASSA ORQALI</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="E368" s="3" t="n">
@@ -23517,10 +23509,14 @@
       <c r="G368" s="3" t="inlineStr"/>
       <c r="H368" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
-        </is>
-      </c>
-      <c r="I368" s="3" t="inlineStr"/>
+          <t>36 oygacha</t>
+        </is>
+      </c>
+      <c r="I368" s="3" t="inlineStr">
+        <is>
+          <t>100 mln gacha</t>
+        </is>
+      </c>
       <c r="J368" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23528,15 +23524,15 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L368" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M368" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L368" s="3" t="inlineStr"/>
+      <c r="M368" s="3" t="inlineStr">
+        <is>
+          <t>Boshlang'ich badal yo'q</t>
+        </is>
+      </c>
       <c r="N368" s="6" t="inlineStr">
         <is>
           <t>https://poytaxtbank.uz/uz/private/crediting/microloan/</t>
@@ -23561,11 +23557,11 @@
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz "Bir to‘lov... YANGI</t>
+          <t>Mikroqarz KASSA ORQALI</t>
         </is>
       </c>
       <c r="E369" s="3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F369" s="3" t="n">
         <v>28</v>
@@ -23595,7 +23591,7 @@
       <c r="M369" s="3" t="inlineStr"/>
       <c r="N369" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/mikroqarz-bir-to-lov/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/microloan/</t>
         </is>
       </c>
     </row>
@@ -23617,22 +23613,22 @@
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>Oylik ish haqi loyihasida Mikroqarz</t>
+          <t>Mikroqarz "Bir to‘lov... YANGI</t>
         </is>
       </c>
       <c r="E370" s="3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F370" s="3" t="n">
         <v>28</v>
       </c>
       <c r="G370" s="3" t="inlineStr"/>
-      <c r="H370" s="3" t="inlineStr"/>
-      <c r="I370" s="3" t="inlineStr">
-        <is>
-          <t>600 ming – 100 mln</t>
-        </is>
-      </c>
+      <c r="H370" s="3" t="inlineStr">
+        <is>
+          <t>3 yilgacha</t>
+        </is>
+      </c>
+      <c r="I370" s="3" t="inlineStr"/>
       <c r="J370" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23651,7 +23647,7 @@
       <c r="M370" s="3" t="inlineStr"/>
       <c r="N370" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/oylik-ish-haqi-loyihasida-mikroqarz/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/mikroqarz-bir-to-lov/</t>
         </is>
       </c>
     </row>
@@ -23663,32 +23659,32 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>Avto kredit</t>
+          <t>Oylik ish haqi loyihasida Mikroqarz</t>
         </is>
       </c>
       <c r="E371" s="3" t="n">
-        <v>27.99</v>
+        <v>20</v>
       </c>
       <c r="F371" s="3" t="n">
-        <v>27.99</v>
+        <v>28</v>
       </c>
       <c r="G371" s="3" t="inlineStr"/>
-      <c r="H371" s="3" t="inlineStr">
-        <is>
-          <t>3 yilgacha</t>
-        </is>
-      </c>
-      <c r="I371" s="3" t="inlineStr"/>
+      <c r="H371" s="3" t="inlineStr"/>
+      <c r="I371" s="3" t="inlineStr">
+        <is>
+          <t>600 ming – 100 mln</t>
+        </is>
+      </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23707,7 +23703,7 @@
       <c r="M371" s="3" t="inlineStr"/>
       <c r="N371" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/avto-kredit-/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/oylik-ish-haqi-loyihasida-mikroqarz/</t>
         </is>
       </c>
     </row>
@@ -23729,7 +23725,7 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>Avto kredit (5 tonnagacha bo‘l... YANGI</t>
+          <t>Avto kredit</t>
         </is>
       </c>
       <c r="E372" s="3" t="n">
@@ -23763,7 +23759,7 @@
       <c r="M372" s="3" t="inlineStr"/>
       <c r="N372" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/avto-kredit-5-tonnagacha-bo-lgan-yo-lovchi-va-yuk-tashish-uchun/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/avto-kredit-/</t>
         </is>
       </c>
     </row>
@@ -23785,7 +23781,7 @@
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>Avto kredit YANGI</t>
+          <t>Avto kredit (5 tonnagacha bo‘l... YANGI</t>
         </is>
       </c>
       <c r="E373" s="3" t="n">
@@ -23819,7 +23815,7 @@
       <c r="M373" s="3" t="inlineStr"/>
       <c r="N373" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/small-business/crediting/avto-kredit-/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/avto-kredit-5-tonnagacha-bo-lgan-yo-lovchi-va-yuk-tashish-uchun/</t>
         </is>
       </c>
     </row>
@@ -23836,12 +23832,12 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>“Faol tadbirkor” krediti YANGI</t>
+          <t>Avto kredit YANGI</t>
         </is>
       </c>
       <c r="E374" s="3" t="n">
@@ -23853,7 +23849,7 @@
       <c r="G374" s="3" t="inlineStr"/>
       <c r="H374" s="3" t="inlineStr">
         <is>
-          <t>1 yilgacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I374" s="3" t="inlineStr"/>
@@ -23875,7 +23871,7 @@
       <c r="M374" s="3" t="inlineStr"/>
       <c r="N374" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/faol-tadbirkor-krediti/</t>
+          <t>https://poytaxtbank.uz/uz/small-business/crediting/avto-kredit-/</t>
         </is>
       </c>
     </row>
@@ -23897,7 +23893,7 @@
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>Revolver kreditlar</t>
+          <t>“Faol tadbirkor” krediti YANGI</t>
         </is>
       </c>
       <c r="E375" s="3" t="n">
@@ -23909,7 +23905,7 @@
       <c r="G375" s="3" t="inlineStr"/>
       <c r="H375" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>1 yilgacha</t>
         </is>
       </c>
       <c r="I375" s="3" t="inlineStr"/>
@@ -23931,7 +23927,7 @@
       <c r="M375" s="3" t="inlineStr"/>
       <c r="N375" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/revolver-kreditlar/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/faol-tadbirkor-krediti/</t>
         </is>
       </c>
     </row>
@@ -23953,7 +23949,7 @@
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>Aylanma mablagʻlarni toʻldiris...</t>
+          <t>Revolver kreditlar</t>
         </is>
       </c>
       <c r="E376" s="3" t="n">
@@ -23987,7 +23983,7 @@
       <c r="M376" s="3" t="inlineStr"/>
       <c r="N376" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/aylanma-mablag-larni-to-ldirish-/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/revolver-kreditlar/</t>
         </is>
       </c>
     </row>
@@ -24009,7 +24005,7 @@
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>Asosiy vosita hamda investitsi...</t>
+          <t>Aylanma mablagʻlarni toʻldiris...</t>
         </is>
       </c>
       <c r="E377" s="3" t="n">
@@ -24043,7 +24039,7 @@
       <c r="M377" s="3" t="inlineStr"/>
       <c r="N377" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/small-business/crediting/asosiy-vosita-hamda-investitsiya-loyihalarni-moliyalashtirish/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/aylanma-mablag-larni-to-ldirish-/</t>
         </is>
       </c>
     </row>
@@ -24065,14 +24061,14 @@
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>Poytaxt Biznes 2 YANGI</t>
+          <t>Asosiy vosita hamda investitsi...</t>
         </is>
       </c>
       <c r="E378" s="3" t="n">
-        <v>25</v>
+        <v>27.99</v>
       </c>
       <c r="F378" s="3" t="n">
-        <v>25</v>
+        <v>27.99</v>
       </c>
       <c r="G378" s="3" t="inlineStr"/>
       <c r="H378" s="3" t="inlineStr">
@@ -24099,7 +24095,7 @@
       <c r="M378" s="3" t="inlineStr"/>
       <c r="N378" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/poytaxt-biznes-2/</t>
+          <t>https://poytaxtbank.uz/uz/small-business/crediting/asosiy-vosita-hamda-investitsiya-loyihalarni-moliyalashtirish/</t>
         </is>
       </c>
     </row>
@@ -24121,7 +24117,7 @@
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>Asosiy vosita hamda investitsi...</t>
+          <t>Poytaxt Biznes 2 YANGI</t>
         </is>
       </c>
       <c r="E379" s="3" t="n">
@@ -24133,7 +24129,7 @@
       <c r="G379" s="3" t="inlineStr"/>
       <c r="H379" s="3" t="inlineStr">
         <is>
-          <t>5 yilgacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I379" s="3" t="inlineStr"/>
@@ -24155,7 +24151,7 @@
       <c r="M379" s="3" t="inlineStr"/>
       <c r="N379" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/asosiy-vosita-hamda-investitsiya-loyihalarni-moliyalashtirish/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/poytaxt-biznes-2/</t>
         </is>
       </c>
     </row>
@@ -24172,24 +24168,24 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>Koʻp qavatli uy-joylar qurish ... YANGI</t>
+          <t>Asosiy vosita hamda investitsi...</t>
         </is>
       </c>
       <c r="E380" s="3" t="n">
-        <v>27.99</v>
+        <v>25</v>
       </c>
       <c r="F380" s="3" t="n">
-        <v>27.99</v>
+        <v>25</v>
       </c>
       <c r="G380" s="3" t="inlineStr"/>
       <c r="H380" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>5 yilgacha</t>
         </is>
       </c>
       <c r="I380" s="3" t="inlineStr"/>
@@ -24211,39 +24207,43 @@
       <c r="M380" s="3" t="inlineStr"/>
       <c r="N380" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/ko-p-qavatli-uy-joylar-qurish-va-rekonstruksiya-qilish-uchun/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/asosiy-vosita-hamda-investitsiya-loyihalarni-moliyalashtirish/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
         <is>
-          <t>Smartbank</t>
+          <t>Poytaxt bank</t>
         </is>
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>Kredit</t>
+          <t>Koʻp qavatli uy-joylar qurish ... YANGI</t>
         </is>
       </c>
       <c r="E381" s="3" t="n">
-        <v>24.99</v>
+        <v>27.99</v>
       </c>
       <c r="F381" s="3" t="n">
-        <v>25.99</v>
+        <v>27.99</v>
       </c>
       <c r="G381" s="3" t="inlineStr"/>
-      <c r="H381" s="3" t="inlineStr"/>
+      <c r="H381" s="3" t="inlineStr">
+        <is>
+          <t>3 yilgacha</t>
+        </is>
+      </c>
       <c r="I381" s="3" t="inlineStr"/>
       <c r="J381" s="3" t="inlineStr">
         <is>
@@ -24252,18 +24252,18 @@
       </c>
       <c r="K381" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L381" s="3" t="inlineStr"/>
-      <c r="M381" s="3" t="inlineStr">
-        <is>
-          <t>Rasmiy daromadli 24.99%, o'zini band qilganlar 25.99%; sahifa 'Openbank' nomida</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L381" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M381" s="3" t="inlineStr"/>
       <c r="N381" s="6" t="inlineStr">
         <is>
-          <t>https://smartbank.uz/useful/faq</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/ko-p-qavatli-uy-joylar-qurish-va-rekonstruksiya-qilish-uchun/</t>
         </is>
       </c>
     </row>
@@ -29336,85 +29336,81 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Orient Finans Bank</t>
+          <t>Openbank</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>12.5 – 30</t>
+          <t>24.99 – 25.99</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>ofb.uz</t>
+          <t>openbank.uz</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Poytaxt bank</t>
+          <t>Orient Finans Bank</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>20 – 31.99</t>
+          <t>12.5 – 30</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>poytaxtbank.uz</t>
+          <t>ofb.uz</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Smartbank</t>
+          <t>Poytaxt bank</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>24.99 – 25.99</t>
+          <t>20 – 31.99</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Sayt 'Openbank' nomida</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>smartbank.uz</t>
+          <t>poytaxtbank.uz</t>
         </is>
       </c>
     </row>

--- a/research/rasmiy-2026-10-14/banklar_kredit_omonat_rasmiy.xlsx
+++ b/research/rasmiy-2026-10-14/banklar_kredit_omonat_rasmiy.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Izoh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kreditlar'!$A$1:$N$451</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kreditlar'!$A$1:$N$453</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Banklar xulosasi'!$A$1:$G$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Izoh'!$A$1:$A$9</definedName>
   </definedNames>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Manba: bank saytlari. 119 ta qo'lda tekshirilgan mahsulot, 30 ta bank.</t>
+          <t>Manba: bank saytlari. 121 ta qo'lda tekshirilgan mahsulot, 30 ta bank.</t>
         </is>
       </c>
     </row>
@@ -1643,56 +1643,64 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Openbank</t>
+          <t>Asakabank</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Kredit</t>
+          <t>Sayohatchi</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>24.99 – 25.99</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr"/>
+          <t>25 – 27</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>6 oy – 1 yil</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>100 mln gacha</t>
+        </is>
+      </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>https://openbank.uz/faq</t>
+          <t>https://bank.uz/uz/credit/puteshestvennik</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Asakabank</t>
+          <t>Hamkorbank</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Sayohatchi</t>
+          <t>Iste'mol krediti</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>25 – 27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 1 yil</t>
+          <t>36 oygacha</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>100 mln gacha</t>
+          <t>200 mln gacha</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>https://bank.uz/uz/credit/puteshestvennik</t>
+          <t>https://hamkorbank.uz/uz/physical/credits/</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N451"/>
+  <dimension ref="A1:N453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -20626,12 +20634,12 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>Kredit</t>
+          <t>Yangi uy</t>
         </is>
       </c>
       <c r="E319" s="3" t="n">
@@ -20641,8 +20649,16 @@
         <v>25.99</v>
       </c>
       <c r="G319" s="3" t="inlineStr"/>
-      <c r="H319" s="3" t="inlineStr"/>
-      <c r="I319" s="3" t="inlineStr"/>
+      <c r="H319" s="3" t="inlineStr">
+        <is>
+          <t>10 yilgacha</t>
+        </is>
+      </c>
+      <c r="I319" s="3" t="inlineStr">
+        <is>
+          <t>1 mlrd gacha</t>
+        </is>
+      </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -20656,19 +20672,19 @@
       <c r="L319" s="3" t="inlineStr"/>
       <c r="M319" s="3" t="inlineStr">
         <is>
-          <t>Rasmiy daromadli 24.99%, o'zini band qilganlar 25.99%</t>
+          <t>Rasmiy daromadli 24.99%, o'zini band qilganlar 25.99% (FAQ); boshlang'ich to'lov 20% dan; onlayn, jarimasiz</t>
         </is>
       </c>
       <c r="N319" s="6" t="inlineStr">
         <is>
-          <t>https://openbank.uz/faq</t>
+          <t>https://openbank.uz/mortgage</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>Orient Finans Bank</t>
+          <t>Openbank</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
@@ -20678,29 +20694,29 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit Ikkilamchi bozorga</t>
+          <t>Open muddatli to'lov (karta)</t>
         </is>
       </c>
       <c r="E320" s="3" t="n">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="F320" s="3" t="n">
-        <v>24.9</v>
+        <v>29.5</v>
       </c>
       <c r="G320" s="3" t="inlineStr"/>
       <c r="H320" s="3" t="inlineStr">
         <is>
-          <t>4 yilgacha</t>
+          <t>3 – 12 oy</t>
         </is>
       </c>
       <c r="I320" s="3" t="inlineStr">
         <is>
-          <t>800 mln gacha</t>
+          <t>100 mln gacha</t>
         </is>
       </c>
       <c r="J320" s="3" t="inlineStr">
@@ -20710,57 +20726,53 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L320" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M320" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L320" s="3" t="inlineStr"/>
+      <c r="M320" s="3" t="inlineStr">
+        <is>
+          <t>Har bir xarid 3–12 oyga bo'linadi, boshlang'ich to'lovsiz; manba: bankxizmatlari.uz (Markaziy bank portali)</t>
+        </is>
+      </c>
       <c r="N320" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/ikkilamchi-bozor-uchun-avtokredit</t>
+          <t>https://bankxizmatlari.uz/uz/loans/consumer-loan/265225/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>Orient Finans Bank</t>
+          <t>Openbank</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit Import</t>
-        </is>
-      </c>
-      <c r="E321" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F321" s="3" t="n">
-        <v>22.9</v>
-      </c>
+          <t>Biznes uchun muddatli to'lov</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="n"/>
+      <c r="F321" s="3" t="n"/>
       <c r="G321" s="3" t="inlineStr"/>
       <c r="H321" s="3" t="inlineStr">
         <is>
-          <t>5 yilgacha</t>
+          <t>24 oygacha</t>
         </is>
       </c>
       <c r="I321" s="3" t="inlineStr">
         <is>
-          <t>800 mln gacha</t>
+          <t>5 mlrd gacha</t>
         </is>
       </c>
       <c r="J321" s="3" t="inlineStr">
@@ -20770,18 +20782,18 @@
       </c>
       <c r="K321" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L321" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M321" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L321" s="3" t="inlineStr"/>
+      <c r="M321" s="3" t="inlineStr">
+        <is>
+          <t>Biznes marketpleysdan tovar xaridi; stavka saytda ko'rsatilmagan; jarima va yashirin to'lov yo'q</t>
+        </is>
+      </c>
       <c r="N321" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/import-avtokredit</t>
+          <t>https://openbank.uz/business/installment</t>
         </is>
       </c>
     </row>
@@ -20803,19 +20815,19 @@
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit Foydali</t>
+          <t>Avtokredit Ikkilamchi bozorga</t>
         </is>
       </c>
       <c r="E322" s="3" t="n">
-        <v>22</v>
+        <v>24.9</v>
       </c>
       <c r="F322" s="3" t="n">
-        <v>22</v>
+        <v>24.9</v>
       </c>
       <c r="G322" s="3" t="inlineStr"/>
       <c r="H322" s="3" t="inlineStr">
         <is>
-          <t>1 yilgacha</t>
+          <t>4 yilgacha</t>
         </is>
       </c>
       <c r="I322" s="3" t="inlineStr">
@@ -20841,7 +20853,7 @@
       <c r="M322" s="3" t="inlineStr"/>
       <c r="N322" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/avtokredit-foydali</t>
+          <t>https://ofb.uz/kreditlar/ikkilamchi-bozor-uchun-avtokredit</t>
         </is>
       </c>
     </row>
@@ -20863,14 +20875,14 @@
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>Oson avtokredit</t>
+          <t>Avtokredit Import</t>
         </is>
       </c>
       <c r="E323" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="F323" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="G323" s="3" t="inlineStr"/>
       <c r="H323" s="3" t="inlineStr">
@@ -20901,7 +20913,7 @@
       <c r="M323" s="3" t="inlineStr"/>
       <c r="N323" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/oson-avtokredit</t>
+          <t>https://ofb.uz/kreditlar/import-avtokredit</t>
         </is>
       </c>
     </row>
@@ -20923,21 +20935,19 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>Byudjet tashkilotlari xodimlari uchun</t>
+          <t>Avtokredit Foydali</t>
         </is>
       </c>
       <c r="E324" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F324" s="3" t="n"/>
-      <c r="G324" s="3" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F324" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G324" s="3" t="inlineStr"/>
       <c r="H324" s="3" t="inlineStr">
         <is>
-          <t>60 oygacha</t>
+          <t>1 yilgacha</t>
         </is>
       </c>
       <c r="I324" s="3" t="inlineStr">
@@ -20952,18 +20962,18 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L324" s="3" t="inlineStr"/>
-      <c r="M324" s="3" t="inlineStr">
-        <is>
-          <t>Boshlang'ich badalga qarab pasayadi</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L324" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M324" s="3" t="inlineStr"/>
       <c r="N324" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/byudjet-tashkilotlari-xodimlari-uchun-avtokredit</t>
+          <t>https://ofb.uz/kreditlar/avtokredit-foydali</t>
         </is>
       </c>
     </row>
@@ -20985,17 +20995,19 @@
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>BYD Special Plus</t>
+          <t>Oson avtokredit</t>
         </is>
       </c>
       <c r="E325" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F325" s="3" t="n"/>
+        <v>21.9</v>
+      </c>
+      <c r="F325" s="3" t="n">
+        <v>21.9</v>
+      </c>
       <c r="G325" s="3" t="inlineStr"/>
       <c r="H325" s="3" t="inlineStr">
         <is>
-          <t>36 / 60 oy</t>
+          <t>5 yilgacha</t>
         </is>
       </c>
       <c r="I325" s="3" t="inlineStr">
@@ -21010,18 +21022,18 @@
       </c>
       <c r="K325" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L325" s="3" t="inlineStr"/>
-      <c r="M325" s="3" t="inlineStr">
-        <is>
-          <t>Yangi BYD avtomobillari</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L325" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M325" s="3" t="inlineStr"/>
       <c r="N325" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/byd-special-plus</t>
+          <t>https://ofb.uz/kreditlar/oson-avtokredit</t>
         </is>
       </c>
     </row>
@@ -21038,29 +21050,31 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>OFB Start</t>
+          <t>Byudjet tashkilotlari xodimlari uchun</t>
         </is>
       </c>
       <c r="E326" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F326" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="G326" s="3" t="inlineStr"/>
+        <v>20.9</v>
+      </c>
+      <c r="F326" s="3" t="n"/>
+      <c r="G326" s="3" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
       <c r="H326" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 3 yil</t>
+          <t>60 oygacha</t>
         </is>
       </c>
       <c r="I326" s="3" t="inlineStr">
         <is>
-          <t>5.33715 mln – 1 mlrd</t>
+          <t>800 mln gacha</t>
         </is>
       </c>
       <c r="J326" s="3" t="inlineStr">
@@ -21070,18 +21084,18 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L326" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M326" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L326" s="3" t="inlineStr"/>
+      <c r="M326" s="3" t="inlineStr">
+        <is>
+          <t>Boshlang'ich badalga qarab pasayadi</t>
+        </is>
+      </c>
       <c r="N326" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-start</t>
+          <t>https://ofb.uz/kreditlar/byudjet-tashkilotlari-xodimlari-uchun-avtokredit</t>
         </is>
       </c>
     </row>
@@ -21098,29 +21112,27 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>OFB Ishonchli</t>
+          <t>BYD Special Plus</t>
         </is>
       </c>
       <c r="E327" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F327" s="3" t="n">
-        <v>28</v>
-      </c>
+        <v>12.5</v>
+      </c>
+      <c r="F327" s="3" t="n"/>
       <c r="G327" s="3" t="inlineStr"/>
       <c r="H327" s="3" t="inlineStr">
         <is>
-          <t>2 oy – 2 yil</t>
+          <t>36 / 60 oy</t>
         </is>
       </c>
       <c r="I327" s="3" t="inlineStr">
         <is>
-          <t>18.0539 mln – 2 mlrd</t>
+          <t>800 mln gacha</t>
         </is>
       </c>
       <c r="J327" s="3" t="inlineStr">
@@ -21130,18 +21142,18 @@
       </c>
       <c r="K327" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L327" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M327" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L327" s="3" t="inlineStr"/>
+      <c r="M327" s="3" t="inlineStr">
+        <is>
+          <t>Yangi BYD avtomobillari</t>
+        </is>
+      </c>
       <c r="N327" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-ishonchli</t>
+          <t>https://ofb.uz/kreditlar/byd-special-plus</t>
         </is>
       </c>
     </row>
@@ -21163,24 +21175,24 @@
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>OFB Cash</t>
+          <t>OFB Start</t>
         </is>
       </c>
       <c r="E328" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F328" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G328" s="3" t="inlineStr"/>
       <c r="H328" s="3" t="inlineStr">
         <is>
-          <t>2 oy – 2 yil</t>
+          <t>3 oy – 3 yil</t>
         </is>
       </c>
       <c r="I328" s="3" t="inlineStr">
         <is>
-          <t>17.9531 mln – 1 mlrd</t>
+          <t>5.33715 mln – 1 mlrd</t>
         </is>
       </c>
       <c r="J328" s="3" t="inlineStr">
@@ -21201,7 +21213,7 @@
       <c r="M328" s="3" t="inlineStr"/>
       <c r="N328" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-cash</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-start</t>
         </is>
       </c>
     </row>
@@ -21223,24 +21235,24 @@
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
-          <t>OFB Kapital</t>
+          <t>OFB Ishonchli</t>
         </is>
       </c>
       <c r="E329" s="3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F329" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G329" s="3" t="inlineStr"/>
       <c r="H329" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 3 yil</t>
+          <t>2 oy – 2 yil</t>
         </is>
       </c>
       <c r="I329" s="3" t="inlineStr">
         <is>
-          <t>9.55301 mln – 3 mlrd</t>
+          <t>18.0539 mln – 2 mlrd</t>
         </is>
       </c>
       <c r="J329" s="3" t="inlineStr">
@@ -21261,7 +21273,7 @@
       <c r="M329" s="3" t="inlineStr"/>
       <c r="N329" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-kapital</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-ishonchli</t>
         </is>
       </c>
     </row>
@@ -21283,24 +21295,24 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>OFB Garant</t>
+          <t>OFB Cash</t>
         </is>
       </c>
       <c r="E330" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F330" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G330" s="3" t="inlineStr"/>
       <c r="H330" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 3 yil</t>
+          <t>2 oy – 2 yil</t>
         </is>
       </c>
       <c r="I330" s="3" t="inlineStr">
         <is>
-          <t>93.75 ming – 5 mln</t>
+          <t>17.9531 mln – 1 mlrd</t>
         </is>
       </c>
       <c r="J330" s="3" t="inlineStr">
@@ -21321,7 +21333,7 @@
       <c r="M330" s="3" t="inlineStr"/>
       <c r="N330" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-garant</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-cash</t>
         </is>
       </c>
     </row>
@@ -21343,24 +21355,24 @@
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>OFB Kelajak</t>
+          <t>OFB Kapital</t>
         </is>
       </c>
       <c r="E331" s="3" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="F331" s="3" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="G331" s="3" t="inlineStr"/>
       <c r="H331" s="3" t="inlineStr">
         <is>
-          <t>2 oy – 2 yil</t>
+          <t>3 oy – 3 yil</t>
         </is>
       </c>
       <c r="I331" s="3" t="inlineStr">
         <is>
-          <t>259.193 ming – 1.64891 mln</t>
+          <t>9.55301 mln – 3 mlrd</t>
         </is>
       </c>
       <c r="J331" s="3" t="inlineStr">
@@ -21381,7 +21393,7 @@
       <c r="M331" s="3" t="inlineStr"/>
       <c r="N331" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-kelajak</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-kapital</t>
         </is>
       </c>
     </row>
@@ -21398,16 +21410,16 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Foydali ipoteka</t>
+          <t>OFB Garant</t>
         </is>
       </c>
       <c r="E332" s="3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F332" s="3" t="n">
         <v>25</v>
@@ -21415,12 +21427,12 @@
       <c r="G332" s="3" t="inlineStr"/>
       <c r="H332" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 20 yil</t>
+          <t>3 oy – 3 yil</t>
         </is>
       </c>
       <c r="I332" s="3" t="inlineStr">
         <is>
-          <t>7.82892 mln – 1.06 mlrd</t>
+          <t>93.75 ming – 5 mln</t>
         </is>
       </c>
       <c r="J332" s="3" t="inlineStr">
@@ -21441,7 +21453,7 @@
       <c r="M332" s="3" t="inlineStr"/>
       <c r="N332" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/foydali-ipoteka</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-garant</t>
         </is>
       </c>
     </row>
@@ -21458,29 +21470,29 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>Uy-joy ta'miri uchun ipoteka</t>
+          <t>OFB Kelajak</t>
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="F333" s="3" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="G333" s="3" t="inlineStr"/>
       <c r="H333" s="3" t="inlineStr">
         <is>
-          <t>10 yilgacha</t>
+          <t>2 oy – 2 yil</t>
         </is>
       </c>
       <c r="I333" s="3" t="inlineStr">
         <is>
-          <t>400 mln gacha</t>
+          <t>259.193 ming – 1.64891 mln</t>
         </is>
       </c>
       <c r="J333" s="3" t="inlineStr">
@@ -21490,14 +21502,18 @@
       </c>
       <c r="K333" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L333" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L333" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M333" s="3" t="inlineStr"/>
       <c r="N333" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/tamirlash-uchun-ipoteka-krediti</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-kelajak</t>
         </is>
       </c>
     </row>
@@ -21519,24 +21535,24 @@
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Ta’mirlash uchun ipoteka krediti</t>
+          <t>Foydali ipoteka</t>
         </is>
       </c>
       <c r="E334" s="3" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F334" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G334" s="3" t="inlineStr"/>
       <c r="H334" s="3" t="inlineStr">
         <is>
-          <t>10 yilgacha</t>
+          <t>6 oy – 20 yil</t>
         </is>
       </c>
       <c r="I334" s="3" t="inlineStr">
         <is>
-          <t>400 mln gacha</t>
+          <t>7.82892 mln – 1.06 mlrd</t>
         </is>
       </c>
       <c r="J334" s="3" t="inlineStr">
@@ -21557,7 +21573,7 @@
       <c r="M334" s="3" t="inlineStr"/>
       <c r="N334" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/tamirlash-uchun-ipoteka-krediti</t>
+          <t>https://ofb.uz/kreditlar/foydali-ipoteka</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21595,7 @@
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>Yashil ipoteka</t>
+          <t>Uy-joy ta'miri uchun ipoteka</t>
         </is>
       </c>
       <c r="E335" s="3" t="n">
@@ -21591,12 +21607,12 @@
       <c r="G335" s="3" t="inlineStr"/>
       <c r="H335" s="3" t="inlineStr">
         <is>
-          <t>7 yilgacha</t>
+          <t>10 yilgacha</t>
         </is>
       </c>
       <c r="I335" s="3" t="inlineStr">
         <is>
-          <t>350 mln gacha</t>
+          <t>400 mln gacha</t>
         </is>
       </c>
       <c r="J335" s="3" t="inlineStr">
@@ -21606,18 +21622,14 @@
       </c>
       <c r="K335" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L335" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L335" s="3" t="inlineStr"/>
       <c r="M335" s="3" t="inlineStr"/>
       <c r="N335" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/yashil-ipoteka</t>
+          <t>https://ofb.uz/kreditlar/tamirlash-uchun-ipoteka-krediti</t>
         </is>
       </c>
     </row>
@@ -21639,24 +21651,24 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Navro‘z ipoteka krediti</t>
+          <t>Ta’mirlash uchun ipoteka krediti</t>
         </is>
       </c>
       <c r="E336" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F336" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G336" s="3" t="inlineStr"/>
       <c r="H336" s="3" t="inlineStr">
         <is>
-          <t>20 yilgacha</t>
+          <t>10 yilgacha</t>
         </is>
       </c>
       <c r="I336" s="3" t="inlineStr">
         <is>
-          <t>1.06 mlrd gacha</t>
+          <t>400 mln gacha</t>
         </is>
       </c>
       <c r="J336" s="3" t="inlineStr">
@@ -21677,7 +21689,7 @@
       <c r="M336" s="3" t="inlineStr"/>
       <c r="N336" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/navroz-ipoteka-krediti</t>
+          <t>https://ofb.uz/kreditlar/tamirlash-uchun-ipoteka-krediti</t>
         </is>
       </c>
     </row>
@@ -21699,24 +21711,24 @@
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>Birlamchi bozor uchun ipoteka 2.0</t>
+          <t>Yashil ipoteka</t>
         </is>
       </c>
       <c r="E337" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F337" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G337" s="3" t="inlineStr"/>
       <c r="H337" s="3" t="inlineStr">
         <is>
-          <t>20 yilgacha</t>
+          <t>7 yilgacha</t>
         </is>
       </c>
       <c r="I337" s="3" t="inlineStr">
         <is>
-          <t>800 mln gacha</t>
+          <t>350 mln gacha</t>
         </is>
       </c>
       <c r="J337" s="3" t="inlineStr">
@@ -21737,7 +21749,7 @@
       <c r="M337" s="3" t="inlineStr"/>
       <c r="N337" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/birlamchi-bozor-uchun-2-0</t>
+          <t>https://ofb.uz/kreditlar/yashil-ipoteka</t>
         </is>
       </c>
     </row>
@@ -21759,24 +21771,24 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka O‘qituvchi</t>
+          <t>Navro‘z ipoteka krediti</t>
         </is>
       </c>
       <c r="E338" s="3" t="n">
-        <v>16.7</v>
+        <v>21</v>
       </c>
       <c r="F338" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G338" s="3" t="inlineStr"/>
       <c r="H338" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 20 yil</t>
+          <t>20 yilgacha</t>
         </is>
       </c>
       <c r="I338" s="3" t="inlineStr">
         <is>
-          <t>8.26814 mln – 496.088 mln</t>
+          <t>1.06 mlrd gacha</t>
         </is>
       </c>
       <c r="J338" s="3" t="inlineStr">
@@ -21797,7 +21809,7 @@
       <c r="M338" s="3" t="inlineStr"/>
       <c r="N338" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/ipoteka-oqituvchi</t>
+          <t>https://ofb.uz/kreditlar/navroz-ipoteka-krediti</t>
         </is>
       </c>
     </row>
@@ -21819,24 +21831,24 @@
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>Oilaviy ipoteka</t>
+          <t>Birlamchi bozor uchun ipoteka 2.0</t>
         </is>
       </c>
       <c r="E339" s="3" t="n">
-        <v>16.7</v>
+        <v>19</v>
       </c>
       <c r="F339" s="3" t="n">
-        <v>16.7</v>
+        <v>19</v>
       </c>
       <c r="G339" s="3" t="inlineStr"/>
       <c r="H339" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 20 yil</t>
+          <t>20 yilgacha</t>
         </is>
       </c>
       <c r="I339" s="3" t="inlineStr">
         <is>
-          <t>8.26814 mln – 496.088 mln</t>
+          <t>800 mln gacha</t>
         </is>
       </c>
       <c r="J339" s="3" t="inlineStr">
@@ -21857,7 +21869,7 @@
       <c r="M339" s="3" t="inlineStr"/>
       <c r="N339" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/oilaviy-ipoteka</t>
+          <t>https://ofb.uz/kreditlar/birlamchi-bozor-uchun-2-0</t>
         </is>
       </c>
     </row>
@@ -21874,29 +21886,29 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Corporate Plus</t>
+          <t>Ipoteka O‘qituvchi</t>
         </is>
       </c>
       <c r="E340" s="3" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="F340" s="3" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G340" s="3" t="inlineStr"/>
       <c r="H340" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>6 oy – 20 yil</t>
         </is>
       </c>
       <c r="I340" s="3" t="inlineStr">
         <is>
-          <t>100 mln gacha</t>
+          <t>8.26814 mln – 496.088 mln</t>
         </is>
       </c>
       <c r="J340" s="3" t="inlineStr">
@@ -21917,7 +21929,7 @@
       <c r="M340" s="3" t="inlineStr"/>
       <c r="N340" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/corporate-plus</t>
+          <t>https://ofb.uz/kreditlar/ipoteka-oqituvchi</t>
         </is>
       </c>
     </row>
@@ -21934,25 +21946,29 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
         <is>
-          <t>Qulay qayta moliyalashtirish</t>
+          <t>Oilaviy ipoteka</t>
         </is>
       </c>
       <c r="E341" s="3" t="n">
-        <v>21</v>
+        <v>16.7</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>21</v>
+        <v>16.7</v>
       </c>
       <c r="G341" s="3" t="inlineStr"/>
-      <c r="H341" s="3" t="inlineStr"/>
+      <c r="H341" s="3" t="inlineStr">
+        <is>
+          <t>6 oy – 20 yil</t>
+        </is>
+      </c>
       <c r="I341" s="3" t="inlineStr">
         <is>
-          <t>1.72392 mln – 1 mlrd</t>
+          <t>8.26814 mln – 496.088 mln</t>
         </is>
       </c>
       <c r="J341" s="3" t="inlineStr">
@@ -21973,7 +21989,7 @@
       <c r="M341" s="3" t="inlineStr"/>
       <c r="N341" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/qulay-qayta-moliyalashtirish</t>
+          <t>https://ofb.uz/kreditlar/oilaviy-ipoteka</t>
         </is>
       </c>
     </row>
@@ -21995,20 +22011,24 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Bashkent</t>
+          <t>Corporate Plus</t>
         </is>
       </c>
       <c r="E342" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G342" s="3" t="inlineStr"/>
-      <c r="H342" s="3" t="inlineStr"/>
+      <c r="H342" s="3" t="inlineStr">
+        <is>
+          <t>3 yilgacha</t>
+        </is>
+      </c>
       <c r="I342" s="3" t="inlineStr">
         <is>
-          <t>1.06 mlrd gacha</t>
+          <t>100 mln gacha</t>
         </is>
       </c>
       <c r="J342" s="3" t="inlineStr">
@@ -22029,7 +22049,7 @@
       <c r="M342" s="3" t="inlineStr"/>
       <c r="N342" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/bashkent</t>
+          <t>https://ofb.uz/kreditlar/corporate-plus</t>
         </is>
       </c>
     </row>
@@ -22046,29 +22066,25 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>Kredit karta</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
         <is>
-          <t>Biznes Karta</t>
+          <t>Qulay qayta moliyalashtirish</t>
         </is>
       </c>
       <c r="E343" s="3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F343" s="3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G343" s="3" t="inlineStr"/>
-      <c r="H343" s="3" t="inlineStr">
-        <is>
-          <t>2 oy – 1 yil</t>
-        </is>
-      </c>
+      <c r="H343" s="3" t="inlineStr"/>
       <c r="I343" s="3" t="inlineStr">
         <is>
-          <t>17.9028 mln – 500 mln</t>
+          <t>1.72392 mln – 1 mlrd</t>
         </is>
       </c>
       <c r="J343" s="3" t="inlineStr">
@@ -22089,7 +22105,7 @@
       <c r="M343" s="3" t="inlineStr"/>
       <c r="N343" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/biznes-karta</t>
+          <t>https://ofb.uz/kreditlar/qulay-qayta-moliyalashtirish</t>
         </is>
       </c>
     </row>
@@ -22106,29 +22122,25 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>Kredit karta</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Biznes Overdraft</t>
+          <t>Bashkent</t>
         </is>
       </c>
       <c r="E344" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F344" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G344" s="3" t="inlineStr"/>
-      <c r="H344" s="3" t="inlineStr">
-        <is>
-          <t>2 oy – 18 oy</t>
-        </is>
-      </c>
+      <c r="H344" s="3" t="inlineStr"/>
       <c r="I344" s="3" t="inlineStr">
         <is>
-          <t>17.9028 mln – 1.5 mlrd</t>
+          <t>1.06 mlrd gacha</t>
         </is>
       </c>
       <c r="J344" s="3" t="inlineStr">
@@ -22149,7 +22161,7 @@
       <c r="M344" s="3" t="inlineStr"/>
       <c r="N344" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/biznes-overdraft</t>
+          <t>https://ofb.uz/kreditlar/bashkent</t>
         </is>
       </c>
     </row>
@@ -22171,24 +22183,24 @@
       </c>
       <c r="D345" s="3" t="inlineStr">
         <is>
-          <t>Overdraft</t>
+          <t>Biznes Karta</t>
         </is>
       </c>
       <c r="E345" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F345" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G345" s="3" t="inlineStr"/>
       <c r="H345" s="3" t="inlineStr">
         <is>
-          <t>2 yilgacha</t>
+          <t>2 oy – 1 yil</t>
         </is>
       </c>
       <c r="I345" s="3" t="inlineStr">
         <is>
-          <t>50 mln gacha</t>
+          <t>17.9028 mln – 500 mln</t>
         </is>
       </c>
       <c r="J345" s="3" t="inlineStr">
@@ -22209,7 +22221,7 @@
       <c r="M345" s="3" t="inlineStr"/>
       <c r="N345" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/overdraft</t>
+          <t>https://ofb.uz/biznes/kreditlar/biznes-karta</t>
         </is>
       </c>
     </row>
@@ -22226,29 +22238,29 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Kredit karta</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Onlayn mikroqarz (ilova)</t>
+          <t>Biznes Overdraft</t>
         </is>
       </c>
       <c r="E346" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F346" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G346" s="3" t="inlineStr"/>
       <c r="H346" s="3" t="inlineStr">
         <is>
-          <t>24 oygacha</t>
+          <t>2 oy – 18 oy</t>
         </is>
       </c>
       <c r="I346" s="3" t="inlineStr">
         <is>
-          <t>50 mln gacha</t>
+          <t>17.9028 mln – 1.5 mlrd</t>
         </is>
       </c>
       <c r="J346" s="3" t="inlineStr">
@@ -22258,14 +22270,18 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L346" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L346" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/en/credits/online-microloan</t>
+          <t>https://ofb.uz/biznes/kreditlar/biznes-overdraft</t>
         </is>
       </c>
     </row>
@@ -22282,22 +22298,26 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Kredit karta</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
         <is>
-          <t>Onlayn mikroqarz</t>
+          <t>Overdraft</t>
         </is>
       </c>
       <c r="E347" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F347" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G347" s="3" t="inlineStr"/>
-      <c r="H347" s="3" t="inlineStr"/>
+      <c r="H347" s="3" t="inlineStr">
+        <is>
+          <t>2 yilgacha</t>
+        </is>
+      </c>
       <c r="I347" s="3" t="inlineStr">
         <is>
           <t>50 mln gacha</t>
@@ -22321,7 +22341,7 @@
       <c r="M347" s="3" t="inlineStr"/>
       <c r="N347" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/onlayn-mikroqarz</t>
+          <t>https://ofb.uz/kreditlar/overdraft</t>
         </is>
       </c>
     </row>
@@ -22343,24 +22363,24 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Kichik biznesga qadam</t>
+          <t>Onlayn mikroqarz (ilova)</t>
         </is>
       </c>
       <c r="E348" s="3" t="n">
-        <v>27.4</v>
+        <v>30</v>
       </c>
       <c r="F348" s="3" t="n">
-        <v>27.4</v>
+        <v>30</v>
       </c>
       <c r="G348" s="3" t="inlineStr"/>
       <c r="H348" s="3" t="inlineStr">
         <is>
-          <t>2 yilgacha</t>
+          <t>24 oygacha</t>
         </is>
       </c>
       <c r="I348" s="3" t="inlineStr">
         <is>
-          <t>5 mln gacha</t>
+          <t>50 mln gacha</t>
         </is>
       </c>
       <c r="J348" s="3" t="inlineStr">
@@ -22370,18 +22390,14 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L348" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L348" s="3" t="inlineStr"/>
       <c r="M348" s="3" t="inlineStr"/>
       <c r="N348" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/kichik-biznesga-qadam-mikrozaymi</t>
+          <t>https://ofb.uz/en/credits/online-microloan</t>
         </is>
       </c>
     </row>
@@ -22403,24 +22419,20 @@
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>O‘simlikchilik</t>
+          <t>Onlayn mikroqarz</t>
         </is>
       </c>
       <c r="E349" s="3" t="n">
-        <v>26.9</v>
+        <v>30</v>
       </c>
       <c r="F349" s="3" t="n">
-        <v>26.9</v>
+        <v>30</v>
       </c>
       <c r="G349" s="3" t="inlineStr"/>
-      <c r="H349" s="3" t="inlineStr">
-        <is>
-          <t>3 yilgacha</t>
-        </is>
-      </c>
+      <c r="H349" s="3" t="inlineStr"/>
       <c r="I349" s="3" t="inlineStr">
         <is>
-          <t>30 mln gacha</t>
+          <t>50 mln gacha</t>
         </is>
       </c>
       <c r="J349" s="3" t="inlineStr">
@@ -22441,7 +22453,7 @@
       <c r="M349" s="3" t="inlineStr"/>
       <c r="N349" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/osimlikchilik-mikrozaymi</t>
+          <t>https://ofb.uz/kreditlar/onlayn-mikroqarz</t>
         </is>
       </c>
     </row>
@@ -22463,24 +22475,24 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Bog‘bon</t>
+          <t>Kichik biznesga qadam</t>
         </is>
       </c>
       <c r="E350" s="3" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="G350" s="3" t="inlineStr"/>
       <c r="H350" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>2 yilgacha</t>
         </is>
       </c>
       <c r="I350" s="3" t="inlineStr">
         <is>
-          <t>20 mln gacha</t>
+          <t>5 mln gacha</t>
         </is>
       </c>
       <c r="J350" s="3" t="inlineStr">
@@ -22501,7 +22513,7 @@
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/bogbon-mikrozaymi</t>
+          <t>https://ofb.uz/kreditlar/kichik-biznesga-qadam-mikrozaymi</t>
         </is>
       </c>
     </row>
@@ -22523,28 +22535,24 @@
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz Ichki turizm</t>
+          <t>O‘simlikchilik</t>
         </is>
       </c>
       <c r="E351" s="3" t="n">
-        <v>26</v>
+        <v>26.9</v>
       </c>
       <c r="F351" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="G351" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+        <v>26.9</v>
+      </c>
+      <c r="G351" s="3" t="inlineStr"/>
       <c r="H351" s="3" t="inlineStr">
         <is>
-          <t>12 oygacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I351" s="3" t="inlineStr">
         <is>
-          <t>15 mln gacha</t>
+          <t>30 mln gacha</t>
         </is>
       </c>
       <c r="J351" s="3" t="inlineStr">
@@ -22554,14 +22562,18 @@
       </c>
       <c r="K351" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L351" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L351" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M351" s="3" t="inlineStr"/>
       <c r="N351" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/mikroqarz-ichki-turizm</t>
+          <t>https://ofb.uz/kreditlar/osimlikchilik-mikrozaymi</t>
         </is>
       </c>
     </row>
@@ -22583,24 +22595,24 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>Start Up</t>
+          <t>Bog‘bon</t>
         </is>
       </c>
       <c r="E352" s="3" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="F352" s="3" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="G352" s="3" t="inlineStr"/>
       <c r="H352" s="3" t="inlineStr">
         <is>
-          <t>1 yilgacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I352" s="3" t="inlineStr">
         <is>
-          <t>15 mln gacha</t>
+          <t>20 mln gacha</t>
         </is>
       </c>
       <c r="J352" s="3" t="inlineStr">
@@ -22621,7 +22633,7 @@
       <c r="M352" s="3" t="inlineStr"/>
       <c r="N352" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/start-up-mikrozaymi</t>
+          <t>https://ofb.uz/kreditlar/bogbon-mikrozaymi</t>
         </is>
       </c>
     </row>
@@ -22643,24 +22655,28 @@
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>Oilaviy biznes</t>
+          <t>Mikroqarz Ichki turizm</t>
         </is>
       </c>
       <c r="E353" s="3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="F353" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G353" s="3" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="G353" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="H353" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>12 oygacha</t>
         </is>
       </c>
       <c r="I353" s="3" t="inlineStr">
         <is>
-          <t>25 mln gacha</t>
+          <t>15 mln gacha</t>
         </is>
       </c>
       <c r="J353" s="3" t="inlineStr">
@@ -22670,18 +22686,14 @@
       </c>
       <c r="K353" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L353" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/oilaviy-biznes-mikrozaymi</t>
+          <t>https://ofb.uz/kreditlar/mikroqarz-ichki-turizm</t>
         </is>
       </c>
     </row>
@@ -22703,24 +22715,24 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Ishonch</t>
+          <t>Start Up</t>
         </is>
       </c>
       <c r="E354" s="3" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="F354" s="3" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="G354" s="3" t="inlineStr"/>
       <c r="H354" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>1 yilgacha</t>
         </is>
       </c>
       <c r="I354" s="3" t="inlineStr">
         <is>
-          <t>100 mln gacha</t>
+          <t>15 mln gacha</t>
         </is>
       </c>
       <c r="J354" s="3" t="inlineStr">
@@ -22741,7 +22753,7 @@
       <c r="M354" s="3" t="inlineStr"/>
       <c r="N354" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/ishonch-mikroqarz</t>
+          <t>https://ofb.uz/kreditlar/start-up-mikrozaymi</t>
         </is>
       </c>
     </row>
@@ -22763,24 +22775,24 @@
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>Green mikroqarz</t>
+          <t>Oilaviy biznes</t>
         </is>
       </c>
       <c r="E355" s="3" t="n">
-        <v>20</v>
+        <v>25.9</v>
       </c>
       <c r="F355" s="3" t="n">
-        <v>20</v>
+        <v>25.9</v>
       </c>
       <c r="G355" s="3" t="inlineStr"/>
       <c r="H355" s="3" t="inlineStr">
         <is>
-          <t>36 oygacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I355" s="3" t="inlineStr">
         <is>
-          <t>5–50 mln</t>
+          <t>25 mln gacha</t>
         </is>
       </c>
       <c r="J355" s="3" t="inlineStr">
@@ -22790,14 +22802,18 @@
       </c>
       <c r="K355" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L355" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L355" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M355" s="3" t="inlineStr"/>
       <c r="N355" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/green-mikroqarz</t>
+          <t>https://ofb.uz/kreditlar/oilaviy-biznes-mikrozaymi</t>
         </is>
       </c>
     </row>
@@ -22814,29 +22830,29 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>Ta'lim</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>Ta’lim uchun</t>
+          <t>Ishonch</t>
         </is>
       </c>
       <c r="E356" s="3" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="F356" s="3" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="G356" s="3" t="inlineStr"/>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t>4 yilgacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I356" s="3" t="inlineStr">
         <is>
-          <t>250 mln gacha</t>
+          <t>100 mln gacha</t>
         </is>
       </c>
       <c r="J356" s="3" t="inlineStr">
@@ -22857,7 +22873,7 @@
       <c r="M356" s="3" t="inlineStr"/>
       <c r="N356" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/kreditlar/talim-uchun-istemol-krediti</t>
+          <t>https://ofb.uz/kreditlar/ishonch-mikroqarz</t>
         </is>
       </c>
     </row>
@@ -22869,36 +22885,34 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
         <is>
-          <t>OFB Express (aylanma mablag')</t>
+          <t>Green mikroqarz</t>
         </is>
       </c>
       <c r="E357" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F357" s="3" t="n"/>
-      <c r="G357" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F357" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G357" s="3" t="inlineStr"/>
       <c r="H357" s="3" t="inlineStr">
         <is>
-          <t>24 oygacha</t>
+          <t>36 oygacha</t>
         </is>
       </c>
       <c r="I357" s="3" t="inlineStr">
         <is>
-          <t>1 mlrd gacha</t>
+          <t>5–50 mln</t>
         </is>
       </c>
       <c r="J357" s="3" t="inlineStr">
@@ -22915,14 +22929,14 @@
       <c r="M357" s="3" t="inlineStr"/>
       <c r="N357" s="6" t="inlineStr">
         <is>
-          <t>https://ofb.uz/biznes/kreditlar/ofb-express</t>
+          <t>https://ofb.uz/kreditlar/green-mikroqarz</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>Poytaxt bank</t>
+          <t>Orient Finans Bank</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
@@ -22932,25 +22946,29 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Ta'lim</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>"Milliy" avtokredit</t>
+          <t>Ta’lim uchun</t>
         </is>
       </c>
       <c r="E358" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F358" s="3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G358" s="3" t="inlineStr"/>
-      <c r="H358" s="3" t="inlineStr"/>
+      <c r="H358" s="3" t="inlineStr">
+        <is>
+          <t>4 yilgacha</t>
+        </is>
+      </c>
       <c r="I358" s="3" t="inlineStr">
         <is>
-          <t>100 mln – 300 mln</t>
+          <t>250 mln gacha</t>
         </is>
       </c>
       <c r="J358" s="3" t="inlineStr">
@@ -22971,42 +22989,48 @@
       <c r="M358" s="3" t="inlineStr"/>
       <c r="N358" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/milliy-avtokredit/</t>
+          <t>https://ofb.uz/kreditlar/talim-uchun-istemol-krediti</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
-          <t>Poytaxt bank</t>
+          <t>Orient Finans Bank</t>
         </is>
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>"Mini Truck Avto" krediti</t>
+          <t>OFB Express (aylanma mablag')</t>
         </is>
       </c>
       <c r="E359" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F359" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="G359" s="3" t="inlineStr"/>
-      <c r="H359" s="3" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="F359" s="3" t="n"/>
+      <c r="G359" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H359" s="3" t="inlineStr">
+        <is>
+          <t>24 oygacha</t>
+        </is>
+      </c>
       <c r="I359" s="3" t="inlineStr">
         <is>
-          <t>1 mln – 450 mln</t>
+          <t>1 mlrd gacha</t>
         </is>
       </c>
       <c r="J359" s="3" t="inlineStr">
@@ -23016,18 +23040,14 @@
       </c>
       <c r="K359" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L359" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L359" s="3" t="inlineStr"/>
       <c r="M359" s="3" t="inlineStr"/>
       <c r="N359" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/mini-truck-avto-krediti/</t>
+          <t>https://ofb.uz/biznes/kreditlar/ofb-express</t>
         </is>
       </c>
     </row>
@@ -23049,22 +23069,22 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>BYD / UzAuto / Hyundai</t>
+          <t>"Milliy" avtokredit</t>
         </is>
       </c>
       <c r="E360" s="3" t="n">
-        <v>24.9</v>
+        <v>20</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>26.9</v>
+        <v>28</v>
       </c>
       <c r="G360" s="3" t="inlineStr"/>
-      <c r="H360" s="3" t="inlineStr">
-        <is>
-          <t>48 oy</t>
-        </is>
-      </c>
-      <c r="I360" s="3" t="inlineStr"/>
+      <c r="H360" s="3" t="inlineStr"/>
+      <c r="I360" s="3" t="inlineStr">
+        <is>
+          <t>100 mln – 300 mln</t>
+        </is>
+      </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23072,18 +23092,18 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L360" s="3" t="inlineStr"/>
-      <c r="M360" s="3" t="inlineStr">
-        <is>
-          <t>Ayrim Chevrolet modellari uchun 0%, 60 oygacha</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L360" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M360" s="3" t="inlineStr"/>
       <c r="N360" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/milliy-avtokredit/</t>
         </is>
       </c>
     </row>
@@ -23105,22 +23125,22 @@
       </c>
       <c r="D361" s="3" t="inlineStr">
         <is>
-          <t>"Komfort AVTO" avtok... YANGI</t>
+          <t>"Mini Truck Avto" krediti</t>
         </is>
       </c>
       <c r="E361" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F361" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G361" s="3" t="inlineStr"/>
-      <c r="H361" s="3" t="inlineStr">
-        <is>
-          <t>5 yilgacha</t>
-        </is>
-      </c>
-      <c r="I361" s="3" t="inlineStr"/>
+      <c r="H361" s="3" t="inlineStr"/>
+      <c r="I361" s="3" t="inlineStr">
+        <is>
+          <t>1 mln – 450 mln</t>
+        </is>
+      </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23139,7 +23159,7 @@
       <c r="M361" s="3" t="inlineStr"/>
       <c r="N361" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/komfort-avto-avtokrediti/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/mini-truck-avto-krediti/</t>
         </is>
       </c>
     </row>
@@ -23156,27 +23176,27 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>"Biznesga birinchi qadam" krediti</t>
+          <t>BYD / UzAuto / Hyundai</t>
         </is>
       </c>
       <c r="E362" s="3" t="n">
-        <v>20</v>
+        <v>24.9</v>
       </c>
       <c r="F362" s="3" t="n">
-        <v>28</v>
+        <v>26.9</v>
       </c>
       <c r="G362" s="3" t="inlineStr"/>
-      <c r="H362" s="3" t="inlineStr"/>
-      <c r="I362" s="3" t="inlineStr">
-        <is>
-          <t>18 ming – 15 mln</t>
-        </is>
-      </c>
+      <c r="H362" s="3" t="inlineStr">
+        <is>
+          <t>48 oy</t>
+        </is>
+      </c>
+      <c r="I362" s="3" t="inlineStr"/>
       <c r="J362" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23184,18 +23204,18 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L362" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M362" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L362" s="3" t="inlineStr"/>
+      <c r="M362" s="3" t="inlineStr">
+        <is>
+          <t>Ayrim Chevrolet modellari uchun 0%, 60 oygacha</t>
+        </is>
+      </c>
       <c r="N362" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/first-step-to-business/</t>
+          <t>https://poytaxtbank.uz/uz/private/</t>
         </is>
       </c>
     </row>
@@ -23212,27 +23232,27 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>"Biznesga ikkinchi qadam" krediti</t>
+          <t>"Komfort AVTO" avtok... YANGI</t>
         </is>
       </c>
       <c r="E363" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F363" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G363" s="3" t="inlineStr"/>
-      <c r="H363" s="3" t="inlineStr"/>
-      <c r="I363" s="3" t="inlineStr">
-        <is>
-          <t>42 ming – 17 mln</t>
-        </is>
-      </c>
+      <c r="H363" s="3" t="inlineStr">
+        <is>
+          <t>5 yilgacha</t>
+        </is>
+      </c>
+      <c r="I363" s="3" t="inlineStr"/>
       <c r="J363" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23251,7 +23271,7 @@
       <c r="M363" s="3" t="inlineStr"/>
       <c r="N363" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/second-step-to-business/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/komfort-avto-avtokrediti/</t>
         </is>
       </c>
     </row>
@@ -23268,27 +23288,27 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>Maskan</t>
+          <t>"Biznesga birinchi qadam" krediti</t>
         </is>
       </c>
       <c r="E364" s="3" t="n">
-        <v>27.99</v>
+        <v>20</v>
       </c>
       <c r="F364" s="3" t="n">
-        <v>31.99</v>
+        <v>28</v>
       </c>
       <c r="G364" s="3" t="inlineStr"/>
-      <c r="H364" s="3" t="inlineStr">
-        <is>
-          <t>5–10 yil</t>
-        </is>
-      </c>
-      <c r="I364" s="3" t="inlineStr"/>
+      <c r="H364" s="3" t="inlineStr"/>
+      <c r="I364" s="3" t="inlineStr">
+        <is>
+          <t>18 ming – 15 mln</t>
+        </is>
+      </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23296,18 +23316,18 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L364" s="3" t="inlineStr"/>
-      <c r="M364" s="3" t="inlineStr">
-        <is>
-          <t>Boshlang'ich badal 25%</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L364" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M364" s="3" t="inlineStr"/>
       <c r="N364" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/mortgage-loan</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/first-step-to-business/</t>
         </is>
       </c>
     </row>
@@ -23324,27 +23344,27 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>«Tayyor Uy» ipoteka krediti YANGI</t>
+          <t>"Biznesga ikkinchi qadam" krediti</t>
         </is>
       </c>
       <c r="E365" s="3" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="F365" s="3" t="n">
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="G365" s="3" t="inlineStr"/>
-      <c r="H365" s="3" t="inlineStr">
-        <is>
-          <t>20 yilgacha</t>
-        </is>
-      </c>
-      <c r="I365" s="3" t="inlineStr"/>
+      <c r="H365" s="3" t="inlineStr"/>
+      <c r="I365" s="3" t="inlineStr">
+        <is>
+          <t>42 ming – 17 mln</t>
+        </is>
+      </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23363,7 +23383,7 @@
       <c r="M365" s="3" t="inlineStr"/>
       <c r="N365" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/tayyor-uy-ipoteka-krediti/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/second-step-to-business/</t>
         </is>
       </c>
     </row>
@@ -23380,24 +23400,24 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol krediti</t>
+          <t>Maskan</t>
         </is>
       </c>
       <c r="E366" s="3" t="n">
-        <v>28</v>
+        <v>27.99</v>
       </c>
       <c r="F366" s="3" t="n">
-        <v>30</v>
+        <v>31.99</v>
       </c>
       <c r="G366" s="3" t="inlineStr"/>
       <c r="H366" s="3" t="inlineStr">
         <is>
-          <t>12–36 oy</t>
+          <t>5–10 yil</t>
         </is>
       </c>
       <c r="I366" s="3" t="inlineStr"/>
@@ -23414,12 +23434,12 @@
       <c r="L366" s="3" t="inlineStr"/>
       <c r="M366" s="3" t="inlineStr">
         <is>
-          <t>'Sayohat' krediti: 28%, 12 oy</t>
+          <t>Boshlang'ich badal 25%</t>
         </is>
       </c>
       <c r="N366" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/mortgage-loan</t>
         </is>
       </c>
     </row>
@@ -23436,27 +23456,27 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>Mahalla loyihasi krediti</t>
+          <t>«Tayyor Uy» ipoteka krediti YANGI</t>
         </is>
       </c>
       <c r="E367" s="3" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="F367" s="3" t="n">
-        <v>28</v>
+        <v>24.5</v>
       </c>
       <c r="G367" s="3" t="inlineStr"/>
-      <c r="H367" s="3" t="inlineStr"/>
-      <c r="I367" s="3" t="inlineStr">
-        <is>
-          <t>18 ming – 30 mln</t>
-        </is>
-      </c>
+      <c r="H367" s="3" t="inlineStr">
+        <is>
+          <t>20 yilgacha</t>
+        </is>
+      </c>
+      <c r="I367" s="3" t="inlineStr"/>
       <c r="J367" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23475,7 +23495,7 @@
       <c r="M367" s="3" t="inlineStr"/>
       <c r="N367" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/mahalla-loyihasi-krediti/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/tayyor-uy-ipoteka-krediti/</t>
         </is>
       </c>
     </row>
@@ -23492,31 +23512,27 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol krediti</t>
         </is>
       </c>
       <c r="E368" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F368" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G368" s="3" t="inlineStr"/>
       <c r="H368" s="3" t="inlineStr">
         <is>
-          <t>36 oygacha</t>
-        </is>
-      </c>
-      <c r="I368" s="3" t="inlineStr">
-        <is>
-          <t>100 mln gacha</t>
-        </is>
-      </c>
+          <t>12–36 oy</t>
+        </is>
+      </c>
+      <c r="I368" s="3" t="inlineStr"/>
       <c r="J368" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23530,12 +23546,12 @@
       <c r="L368" s="3" t="inlineStr"/>
       <c r="M368" s="3" t="inlineStr">
         <is>
-          <t>Boshlang'ich badal yo'q</t>
+          <t>'Sayohat' krediti: 28%, 12 oy</t>
         </is>
       </c>
       <c r="N368" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/microloan/</t>
+          <t>https://poytaxtbank.uz/uz/private/</t>
         </is>
       </c>
     </row>
@@ -23552,27 +23568,27 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz KASSA ORQALI</t>
+          <t>Mahalla loyihasi krediti</t>
         </is>
       </c>
       <c r="E369" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F369" s="3" t="n">
         <v>28</v>
       </c>
       <c r="G369" s="3" t="inlineStr"/>
-      <c r="H369" s="3" t="inlineStr">
-        <is>
-          <t>3 yilgacha</t>
-        </is>
-      </c>
-      <c r="I369" s="3" t="inlineStr"/>
+      <c r="H369" s="3" t="inlineStr"/>
+      <c r="I369" s="3" t="inlineStr">
+        <is>
+          <t>18 ming – 30 mln</t>
+        </is>
+      </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23591,7 +23607,7 @@
       <c r="M369" s="3" t="inlineStr"/>
       <c r="N369" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/microloan/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/mahalla-loyihasi-krediti/</t>
         </is>
       </c>
     </row>
@@ -23613,11 +23629,11 @@
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz "Bir to‘lov... YANGI</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="E370" s="3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F370" s="3" t="n">
         <v>28</v>
@@ -23625,10 +23641,14 @@
       <c r="G370" s="3" t="inlineStr"/>
       <c r="H370" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
-        </is>
-      </c>
-      <c r="I370" s="3" t="inlineStr"/>
+          <t>36 oygacha</t>
+        </is>
+      </c>
+      <c r="I370" s="3" t="inlineStr">
+        <is>
+          <t>100 mln gacha</t>
+        </is>
+      </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23636,18 +23656,18 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L370" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M370" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L370" s="3" t="inlineStr"/>
+      <c r="M370" s="3" t="inlineStr">
+        <is>
+          <t>Boshlang'ich badal yo'q</t>
+        </is>
+      </c>
       <c r="N370" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/mikroqarz-bir-to-lov/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/microloan/</t>
         </is>
       </c>
     </row>
@@ -23669,22 +23689,22 @@
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>Oylik ish haqi loyihasida Mikroqarz</t>
+          <t>Mikroqarz KASSA ORQALI</t>
         </is>
       </c>
       <c r="E371" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F371" s="3" t="n">
         <v>28</v>
       </c>
       <c r="G371" s="3" t="inlineStr"/>
-      <c r="H371" s="3" t="inlineStr"/>
-      <c r="I371" s="3" t="inlineStr">
-        <is>
-          <t>600 ming – 100 mln</t>
-        </is>
-      </c>
+      <c r="H371" s="3" t="inlineStr">
+        <is>
+          <t>3 yilgacha</t>
+        </is>
+      </c>
+      <c r="I371" s="3" t="inlineStr"/>
       <c r="J371" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23703,7 +23723,7 @@
       <c r="M371" s="3" t="inlineStr"/>
       <c r="N371" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/private/crediting/oylik-ish-haqi-loyihasida-mikroqarz/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/microloan/</t>
         </is>
       </c>
     </row>
@@ -23715,24 +23735,24 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>Avto kredit</t>
+          <t>Mikroqarz "Bir to‘lov... YANGI</t>
         </is>
       </c>
       <c r="E372" s="3" t="n">
-        <v>27.99</v>
+        <v>28</v>
       </c>
       <c r="F372" s="3" t="n">
-        <v>27.99</v>
+        <v>28</v>
       </c>
       <c r="G372" s="3" t="inlineStr"/>
       <c r="H372" s="3" t="inlineStr">
@@ -23759,7 +23779,7 @@
       <c r="M372" s="3" t="inlineStr"/>
       <c r="N372" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/avto-kredit-/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/mikroqarz-bir-to-lov/</t>
         </is>
       </c>
     </row>
@@ -23771,32 +23791,32 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>Avto kredit (5 tonnagacha bo‘l... YANGI</t>
+          <t>Oylik ish haqi loyihasida Mikroqarz</t>
         </is>
       </c>
       <c r="E373" s="3" t="n">
-        <v>27.99</v>
+        <v>20</v>
       </c>
       <c r="F373" s="3" t="n">
-        <v>27.99</v>
+        <v>28</v>
       </c>
       <c r="G373" s="3" t="inlineStr"/>
-      <c r="H373" s="3" t="inlineStr">
-        <is>
-          <t>3 yilgacha</t>
-        </is>
-      </c>
-      <c r="I373" s="3" t="inlineStr"/>
+      <c r="H373" s="3" t="inlineStr"/>
+      <c r="I373" s="3" t="inlineStr">
+        <is>
+          <t>600 ming – 100 mln</t>
+        </is>
+      </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -23815,7 +23835,7 @@
       <c r="M373" s="3" t="inlineStr"/>
       <c r="N373" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/avto-kredit-5-tonnagacha-bo-lgan-yo-lovchi-va-yuk-tashish-uchun/</t>
+          <t>https://poytaxtbank.uz/uz/private/crediting/oylik-ish-haqi-loyihasida-mikroqarz/</t>
         </is>
       </c>
     </row>
@@ -23837,7 +23857,7 @@
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>Avto kredit YANGI</t>
+          <t>Avto kredit</t>
         </is>
       </c>
       <c r="E374" s="3" t="n">
@@ -23871,7 +23891,7 @@
       <c r="M374" s="3" t="inlineStr"/>
       <c r="N374" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/small-business/crediting/avto-kredit-/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/avto-kredit-/</t>
         </is>
       </c>
     </row>
@@ -23888,12 +23908,12 @@
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>“Faol tadbirkor” krediti YANGI</t>
+          <t>Avto kredit (5 tonnagacha bo‘l... YANGI</t>
         </is>
       </c>
       <c r="E375" s="3" t="n">
@@ -23905,7 +23925,7 @@
       <c r="G375" s="3" t="inlineStr"/>
       <c r="H375" s="3" t="inlineStr">
         <is>
-          <t>1 yilgacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I375" s="3" t="inlineStr"/>
@@ -23927,7 +23947,7 @@
       <c r="M375" s="3" t="inlineStr"/>
       <c r="N375" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/faol-tadbirkor-krediti/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/avto-kredit-5-tonnagacha-bo-lgan-yo-lovchi-va-yuk-tashish-uchun/</t>
         </is>
       </c>
     </row>
@@ -23944,12 +23964,12 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>Revolver kreditlar</t>
+          <t>Avto kredit YANGI</t>
         </is>
       </c>
       <c r="E376" s="3" t="n">
@@ -23983,7 +24003,7 @@
       <c r="M376" s="3" t="inlineStr"/>
       <c r="N376" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/revolver-kreditlar/</t>
+          <t>https://poytaxtbank.uz/uz/small-business/crediting/avto-kredit-/</t>
         </is>
       </c>
     </row>
@@ -24005,7 +24025,7 @@
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>Aylanma mablagʻlarni toʻldiris...</t>
+          <t>“Faol tadbirkor” krediti YANGI</t>
         </is>
       </c>
       <c r="E377" s="3" t="n">
@@ -24017,7 +24037,7 @@
       <c r="G377" s="3" t="inlineStr"/>
       <c r="H377" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>1 yilgacha</t>
         </is>
       </c>
       <c r="I377" s="3" t="inlineStr"/>
@@ -24039,7 +24059,7 @@
       <c r="M377" s="3" t="inlineStr"/>
       <c r="N377" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/aylanma-mablag-larni-to-ldirish-/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/faol-tadbirkor-krediti/</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24081,7 @@
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>Asosiy vosita hamda investitsi...</t>
+          <t>Revolver kreditlar</t>
         </is>
       </c>
       <c r="E378" s="3" t="n">
@@ -24095,7 +24115,7 @@
       <c r="M378" s="3" t="inlineStr"/>
       <c r="N378" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/small-business/crediting/asosiy-vosita-hamda-investitsiya-loyihalarni-moliyalashtirish/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/revolver-kreditlar/</t>
         </is>
       </c>
     </row>
@@ -24117,14 +24137,14 @@
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>Poytaxt Biznes 2 YANGI</t>
+          <t>Aylanma mablagʻlarni toʻldiris...</t>
         </is>
       </c>
       <c r="E379" s="3" t="n">
-        <v>25</v>
+        <v>27.99</v>
       </c>
       <c r="F379" s="3" t="n">
-        <v>25</v>
+        <v>27.99</v>
       </c>
       <c r="G379" s="3" t="inlineStr"/>
       <c r="H379" s="3" t="inlineStr">
@@ -24151,7 +24171,7 @@
       <c r="M379" s="3" t="inlineStr"/>
       <c r="N379" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/poytaxt-biznes-2/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/aylanma-mablag-larni-to-ldirish-/</t>
         </is>
       </c>
     </row>
@@ -24177,15 +24197,15 @@
         </is>
       </c>
       <c r="E380" s="3" t="n">
-        <v>25</v>
+        <v>27.99</v>
       </c>
       <c r="F380" s="3" t="n">
-        <v>25</v>
+        <v>27.99</v>
       </c>
       <c r="G380" s="3" t="inlineStr"/>
       <c r="H380" s="3" t="inlineStr">
         <is>
-          <t>5 yilgacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I380" s="3" t="inlineStr"/>
@@ -24207,7 +24227,7 @@
       <c r="M380" s="3" t="inlineStr"/>
       <c r="N380" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/asosiy-vosita-hamda-investitsiya-loyihalarni-moliyalashtirish/</t>
+          <t>https://poytaxtbank.uz/uz/small-business/crediting/asosiy-vosita-hamda-investitsiya-loyihalarni-moliyalashtirish/</t>
         </is>
       </c>
     </row>
@@ -24224,19 +24244,19 @@
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>Koʻp qavatli uy-joylar qurish ... YANGI</t>
+          <t>Poytaxt Biznes 2 YANGI</t>
         </is>
       </c>
       <c r="E381" s="3" t="n">
-        <v>27.99</v>
+        <v>25</v>
       </c>
       <c r="F381" s="3" t="n">
-        <v>27.99</v>
+        <v>25</v>
       </c>
       <c r="G381" s="3" t="inlineStr"/>
       <c r="H381" s="3" t="inlineStr">
@@ -24263,48 +24283,44 @@
       <c r="M381" s="3" t="inlineStr"/>
       <c r="N381" s="6" t="inlineStr">
         <is>
-          <t>https://poytaxtbank.uz/uz/corporate/crediting/ko-p-qavatli-uy-joylar-qurish-va-rekonstruksiya-qilish-uchun/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/poytaxt-biznes-2/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
         <is>
-          <t>TBC Bank</t>
+          <t>Poytaxt bank</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>TBC Avtokredit</t>
+          <t>Asosiy vosita hamda investitsi...</t>
         </is>
       </c>
       <c r="E382" s="3" t="n">
-        <v>29.5</v>
+        <v>25</v>
       </c>
       <c r="F382" s="3" t="n">
-        <v>29.5</v>
+        <v>25</v>
       </c>
       <c r="G382" s="3" t="inlineStr"/>
       <c r="H382" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 5 yil</t>
-        </is>
-      </c>
-      <c r="I382" s="3" t="inlineStr">
-        <is>
-          <t>1 mlrd gacha</t>
-        </is>
-      </c>
+          <t>5 yilgacha</t>
+        </is>
+      </c>
+      <c r="I382" s="3" t="inlineStr"/>
       <c r="J382" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -24323,48 +24339,44 @@
       <c r="M382" s="3" t="inlineStr"/>
       <c r="N382" s="6" t="inlineStr">
         <is>
-          <t>https://tbcbank.uz/product/avtokredit/tariffs/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/asosiy-vosita-hamda-investitsiya-loyihalarni-moliyalashtirish/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
         <is>
-          <t>TBC Bank</t>
+          <t>Poytaxt bank</t>
         </is>
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>Kredit biznesning o‘sishiga qanday yordam beradi: 6 ta misol</t>
+          <t>Koʻp qavatli uy-joylar qurish ... YANGI</t>
         </is>
       </c>
       <c r="E383" s="3" t="n">
-        <v>33</v>
+        <v>27.99</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>38</v>
+        <v>27.99</v>
       </c>
       <c r="G383" s="3" t="inlineStr"/>
       <c r="H383" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 3 yil</t>
-        </is>
-      </c>
-      <c r="I383" s="3" t="inlineStr">
-        <is>
-          <t>10 mln – 300 mln</t>
-        </is>
-      </c>
+          <t>3 yilgacha</t>
+        </is>
+      </c>
+      <c r="I383" s="3" t="inlineStr"/>
       <c r="J383" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -24383,7 +24395,7 @@
       <c r="M383" s="3" t="inlineStr"/>
       <c r="N383" s="6" t="inlineStr">
         <is>
-          <t>https://tbcbank.uz/blog/articles/kredit-dlya-biznesa-uz/</t>
+          <t>https://poytaxtbank.uz/uz/corporate/crediting/ko-p-qavatli-uy-joylar-qurish-va-rekonstruksiya-qilish-uchun/</t>
         </is>
       </c>
     </row>
@@ -24400,29 +24412,29 @@
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>Bank nima uchun kreditni rad etadi</t>
+          <t>TBC Avtokredit</t>
         </is>
       </c>
       <c r="E384" s="3" t="n">
-        <v>50</v>
+        <v>29.5</v>
       </c>
       <c r="F384" s="3" t="n">
-        <v>50</v>
+        <v>29.5</v>
       </c>
       <c r="G384" s="3" t="inlineStr"/>
       <c r="H384" s="3" t="inlineStr">
         <is>
-          <t>1 oygacha</t>
+          <t>6 oy – 5 yil</t>
         </is>
       </c>
       <c r="I384" s="3" t="inlineStr">
         <is>
-          <t>100 mln gacha</t>
+          <t>1 mlrd gacha</t>
         </is>
       </c>
       <c r="J384" s="3" t="inlineStr">
@@ -24443,7 +24455,7 @@
       <c r="M384" s="3" t="inlineStr"/>
       <c r="N384" s="6" t="inlineStr">
         <is>
-          <t>https://tbcbank.uz/blog/articles/pochemu-banki-otkazivayut-v-kredite-uz/</t>
+          <t>https://tbcbank.uz/product/avtokredit/tariffs/</t>
         </is>
       </c>
     </row>
@@ -24460,23 +24472,31 @@
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>Kredit karta</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>TBC Osmon</t>
-        </is>
-      </c>
-      <c r="E385" s="3" t="n"/>
-      <c r="F385" s="3" t="n"/>
+          <t>Kredit biznesning o‘sishiga qanday yordam beradi: 6 ta misol</t>
+        </is>
+      </c>
+      <c r="E385" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F385" s="3" t="n">
+        <v>38</v>
+      </c>
       <c r="G385" s="3" t="inlineStr"/>
       <c r="H385" s="3" t="inlineStr">
         <is>
-          <t>Imtiyozli davr 25–55 kun</t>
-        </is>
-      </c>
-      <c r="I385" s="3" t="inlineStr"/>
+          <t>3 oy – 3 yil</t>
+        </is>
+      </c>
+      <c r="I385" s="3" t="inlineStr">
+        <is>
+          <t>10 mln – 300 mln</t>
+        </is>
+      </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -24484,18 +24504,18 @@
       </c>
       <c r="K385" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L385" s="3" t="inlineStr"/>
-      <c r="M385" s="3" t="inlineStr">
-        <is>
-          <t>Stavka ilovadagi 'Shartlar' bo'limida</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L385" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M385" s="3" t="inlineStr"/>
       <c r="N385" s="6" t="inlineStr">
         <is>
-          <t>https://tbcbank.uz/product/credit-card/</t>
+          <t>https://tbcbank.uz/blog/articles/kredit-dlya-biznesa-uz/</t>
         </is>
       </c>
     </row>
@@ -24512,24 +24532,24 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Onlayn kredit (ilova orqali)</t>
+          <t>Bank nima uchun kreditni rad etadi</t>
         </is>
       </c>
       <c r="E386" s="3" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F386" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G386" s="3" t="inlineStr"/>
       <c r="H386" s="3" t="inlineStr">
         <is>
-          <t>3–36 oy</t>
+          <t>1 oygacha</t>
         </is>
       </c>
       <c r="I386" s="3" t="inlineStr">
@@ -24544,18 +24564,18 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L386" s="3" t="inlineStr"/>
-      <c r="M386" s="3" t="inlineStr">
-        <is>
-          <t>Stavka mijoz profiliga qarab</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L386" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M386" s="3" t="inlineStr"/>
       <c r="N386" s="6" t="inlineStr">
         <is>
-          <t>https://tbcbank.uz/product/kredity/</t>
+          <t>https://tbcbank.uz/blog/articles/pochemu-banki-otkazivayut-v-kredite-uz/</t>
         </is>
       </c>
     </row>
@@ -24572,22 +24592,22 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Kredit karta</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
         <is>
-          <t>Mikrokredit</t>
-        </is>
-      </c>
-      <c r="E387" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="F387" s="3" t="n">
-        <v>48</v>
-      </c>
+          <t>TBC Osmon</t>
+        </is>
+      </c>
+      <c r="E387" s="3" t="n"/>
+      <c r="F387" s="3" t="n"/>
       <c r="G387" s="3" t="inlineStr"/>
-      <c r="H387" s="3" t="inlineStr"/>
+      <c r="H387" s="3" t="inlineStr">
+        <is>
+          <t>Imtiyozli davr 25–55 kun</t>
+        </is>
+      </c>
       <c r="I387" s="3" t="inlineStr"/>
       <c r="J387" s="3" t="inlineStr">
         <is>
@@ -24600,10 +24620,14 @@
         </is>
       </c>
       <c r="L387" s="3" t="inlineStr"/>
-      <c r="M387" s="3" t="inlineStr"/>
+      <c r="M387" s="3" t="inlineStr">
+        <is>
+          <t>Stavka ilovadagi 'Shartlar' bo'limida</t>
+        </is>
+      </c>
       <c r="N387" s="6" t="inlineStr">
         <is>
-          <t>https://tbcbank.uz/product/mikrokredit/</t>
+          <t>https://tbcbank.uz/product/credit-card/</t>
         </is>
       </c>
     </row>
@@ -24615,34 +24639,34 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>Biznes uchun garov evaziga kredit</t>
+          <t>Onlayn kredit (ilova orqali)</t>
         </is>
       </c>
       <c r="E388" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F388" s="3" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G388" s="3" t="inlineStr"/>
       <c r="H388" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 7 yil</t>
+          <t>3–36 oy</t>
         </is>
       </c>
       <c r="I388" s="3" t="inlineStr">
         <is>
-          <t>106.514 mln – 12 mlrd</t>
+          <t>100 mln gacha</t>
         </is>
       </c>
       <c r="J388" s="3" t="inlineStr">
@@ -24652,25 +24676,25 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L388" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M388" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L388" s="3" t="inlineStr"/>
+      <c r="M388" s="3" t="inlineStr">
+        <is>
+          <t>Stavka mijoz profiliga qarab</t>
+        </is>
+      </c>
       <c r="N388" s="6" t="inlineStr">
         <is>
-          <t>https://tbcbank.uz/business/product/secured-loan-12-billion/</t>
+          <t>https://tbcbank.uz/product/kredity/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
         <is>
-          <t>Tenge Bank</t>
+          <t>TBC Bank</t>
         </is>
       </c>
       <c r="B389" s="3" t="inlineStr">
@@ -24680,26 +24704,22 @@
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
         <is>
-          <t>Аvtokredit - «ROODELL»</t>
+          <t>Mikrokredit</t>
         </is>
       </c>
       <c r="E389" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F389" s="3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G389" s="3" t="inlineStr"/>
-      <c r="H389" s="3" t="inlineStr">
-        <is>
-          <t>5 yilgacha</t>
-        </is>
-      </c>
+      <c r="H389" s="3" t="inlineStr"/>
       <c r="I389" s="3" t="inlineStr"/>
       <c r="J389" s="3" t="inlineStr">
         <is>
@@ -24708,55 +24728,55 @@
       </c>
       <c r="K389" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L389" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L389" s="3" t="inlineStr"/>
       <c r="M389" s="3" t="inlineStr"/>
       <c r="N389" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/credit/avtokredit-roodell-i</t>
+          <t>https://tbcbank.uz/product/mikrokredit/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
         <is>
-          <t>Tenge Bank</t>
+          <t>TBC Bank</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>Yangi avtomobil uchun avtokredit</t>
+          <t>Biznes uchun garov evaziga kredit</t>
         </is>
       </c>
       <c r="E390" s="3" t="n">
-        <v>22.9</v>
+        <v>22</v>
       </c>
       <c r="F390" s="3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G390" s="3" t="inlineStr"/>
       <c r="H390" s="3" t="inlineStr">
         <is>
-          <t>4 yilgacha</t>
-        </is>
-      </c>
-      <c r="I390" s="3" t="inlineStr"/>
+          <t>6 oy – 7 yil</t>
+        </is>
+      </c>
+      <c r="I390" s="3" t="inlineStr">
+        <is>
+          <t>106.514 mln – 12 mlrd</t>
+        </is>
+      </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -24775,7 +24795,7 @@
       <c r="M390" s="3" t="inlineStr"/>
       <c r="N390" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/credit/avtokredit-na-novyj-avtomobil</t>
+          <t>https://tbcbank.uz/business/product/secured-loan-12-billion/</t>
         </is>
       </c>
     </row>
@@ -24797,26 +24817,22 @@
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit Drive</t>
-        </is>
-      </c>
-      <c r="E391" s="3" t="n"/>
-      <c r="F391" s="3" t="n"/>
-      <c r="G391" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>Аvtokredit - «ROODELL»</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F391" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G391" s="3" t="inlineStr"/>
       <c r="H391" s="3" t="inlineStr">
         <is>
           <t>5 yilgacha</t>
         </is>
       </c>
-      <c r="I391" s="3" t="inlineStr">
-        <is>
-          <t>500 mln gacha</t>
-        </is>
-      </c>
+      <c r="I391" s="3" t="inlineStr"/>
       <c r="J391" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -24824,18 +24840,18 @@
       </c>
       <c r="K391" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L391" s="3" t="inlineStr"/>
-      <c r="M391" s="3" t="inlineStr">
-        <is>
-          <t>Stavka badal va muddatga qarab</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L391" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M391" s="3" t="inlineStr"/>
       <c r="N391" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/en/credit/avtokredit-drive</t>
+          <t>https://tengebank.uz/credit/avtokredit-roodell-i</t>
         </is>
       </c>
     </row>
@@ -24852,31 +24868,27 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>Biznesga birinchi qadam</t>
+          <t>Yangi avtomobil uchun avtokredit</t>
         </is>
       </c>
       <c r="E392" s="3" t="n">
-        <v>25</v>
+        <v>22.9</v>
       </c>
       <c r="F392" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G392" s="3" t="inlineStr"/>
       <c r="H392" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
-        </is>
-      </c>
-      <c r="I392" s="3" t="inlineStr">
-        <is>
-          <t>30 mln gacha</t>
-        </is>
-      </c>
+          <t>4 yilgacha</t>
+        </is>
+      </c>
+      <c r="I392" s="3" t="inlineStr"/>
       <c r="J392" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -24895,7 +24907,7 @@
       <c r="M392" s="3" t="inlineStr"/>
       <c r="N392" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/credit/pervyj-shag-k-biznesu</t>
+          <t>https://tengebank.uz/credit/avtokredit-na-novyj-avtomobil</t>
         </is>
       </c>
     </row>
@@ -24912,27 +24924,31 @@
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>Yangi turarjoyga ipoteka</t>
-        </is>
-      </c>
-      <c r="E393" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="F393" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G393" s="3" t="inlineStr"/>
+          <t>Avtokredit Drive</t>
+        </is>
+      </c>
+      <c r="E393" s="3" t="n"/>
+      <c r="F393" s="3" t="n"/>
+      <c r="G393" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="H393" s="3" t="inlineStr">
         <is>
-          <t>15 yilgacha</t>
-        </is>
-      </c>
-      <c r="I393" s="3" t="inlineStr"/>
+          <t>5 yilgacha</t>
+        </is>
+      </c>
+      <c r="I393" s="3" t="inlineStr">
+        <is>
+          <t>500 mln gacha</t>
+        </is>
+      </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -24940,18 +24956,18 @@
       </c>
       <c r="K393" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L393" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M393" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L393" s="3" t="inlineStr"/>
+      <c r="M393" s="3" t="inlineStr">
+        <is>
+          <t>Stavka badal va muddatga qarab</t>
+        </is>
+      </c>
       <c r="N393" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/credit/ipoteka-na-novoe-jilyo</t>
+          <t>https://tengebank.uz/en/credit/avtokredit-drive</t>
         </is>
       </c>
     </row>
@@ -24968,27 +24984,31 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>Ikkilamchi uy-joy uchun ipoteka</t>
+          <t>Biznesga birinchi qadam</t>
         </is>
       </c>
       <c r="E394" s="3" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="F394" s="3" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="G394" s="3" t="inlineStr"/>
       <c r="H394" s="3" t="inlineStr">
         <is>
-          <t>10 yilgacha</t>
-        </is>
-      </c>
-      <c r="I394" s="3" t="inlineStr"/>
+          <t>3 yilgacha</t>
+        </is>
+      </c>
+      <c r="I394" s="3" t="inlineStr">
+        <is>
+          <t>30 mln gacha</t>
+        </is>
+      </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -24996,18 +25016,18 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L394" s="3" t="inlineStr"/>
-      <c r="M394" s="3" t="inlineStr">
-        <is>
-          <t>Boshlang'ich badal 25%</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L394" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M394" s="3" t="inlineStr"/>
       <c r="N394" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/en/credit/ipoteka-na-vtorichnoe-zhile</t>
+          <t>https://tengebank.uz/credit/pervyj-shag-k-biznesu</t>
         </is>
       </c>
     </row>
@@ -25029,14 +25049,14 @@
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>Yangi uy-joy uchun ipoteka</t>
+          <t>Yangi turarjoyga ipoteka</t>
         </is>
       </c>
       <c r="E395" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="F395" s="3" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="G395" s="3" t="inlineStr"/>
       <c r="H395" s="3" t="inlineStr">
@@ -25052,18 +25072,18 @@
       </c>
       <c r="K395" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L395" s="3" t="inlineStr"/>
-      <c r="M395" s="3" t="inlineStr">
-        <is>
-          <t>Boshlang'ich badal 25%</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L395" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M395" s="3" t="inlineStr"/>
       <c r="N395" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/en/credits</t>
+          <t>https://tengebank.uz/credit/ipoteka-na-novoe-jilyo</t>
         </is>
       </c>
     </row>
@@ -25080,31 +25100,27 @@
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Onlayn mikroqarz</t>
+          <t>Ikkilamchi uy-joy uchun ipoteka</t>
         </is>
       </c>
       <c r="E396" s="3" t="n">
-        <v>24.6</v>
+        <v>23.9</v>
       </c>
       <c r="F396" s="3" t="n">
-        <v>49</v>
+        <v>23.9</v>
       </c>
       <c r="G396" s="3" t="inlineStr"/>
       <c r="H396" s="3" t="inlineStr">
         <is>
-          <t>6–36 oy</t>
-        </is>
-      </c>
-      <c r="I396" s="3" t="inlineStr">
-        <is>
-          <t>1–90 mln</t>
-        </is>
-      </c>
+          <t>10 yilgacha</t>
+        </is>
+      </c>
+      <c r="I396" s="3" t="inlineStr"/>
       <c r="J396" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -25118,12 +25134,12 @@
       <c r="L396" s="3" t="inlineStr"/>
       <c r="M396" s="3" t="inlineStr">
         <is>
-          <t>Kreditlar ro'yxatida '30% dan' deb ko'rsatilgan</t>
+          <t>Boshlang'ich badal 25%</t>
         </is>
       </c>
       <c r="N396" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/en/credit/mikrozajm-onlajn</t>
+          <t>https://tengebank.uz/en/credit/ipoteka-na-vtorichnoe-zhile</t>
         </is>
       </c>
     </row>
@@ -25140,31 +25156,27 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>Onlayn mikroqarz</t>
+          <t>Yangi uy-joy uchun ipoteka</t>
         </is>
       </c>
       <c r="E397" s="3" t="n">
-        <v>24.6</v>
+        <v>23.9</v>
       </c>
       <c r="F397" s="3" t="n">
-        <v>24.6</v>
+        <v>23.9</v>
       </c>
       <c r="G397" s="3" t="inlineStr"/>
       <c r="H397" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
-        </is>
-      </c>
-      <c r="I397" s="3" t="inlineStr">
-        <is>
-          <t>90 mln gacha</t>
-        </is>
-      </c>
+          <t>15 yilgacha</t>
+        </is>
+      </c>
+      <c r="I397" s="3" t="inlineStr"/>
       <c r="J397" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -25172,18 +25184,18 @@
       </c>
       <c r="K397" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L397" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M397" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L397" s="3" t="inlineStr"/>
+      <c r="M397" s="3" t="inlineStr">
+        <is>
+          <t>Boshlang'ich badal 25%</t>
+        </is>
+      </c>
       <c r="N397" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/credit/mikrozajm-onlajn</t>
+          <t>https://tengebank.uz/en/credits</t>
         </is>
       </c>
     </row>
@@ -25195,30 +25207,34 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>Tezkor biznes</t>
+          <t>Onlayn mikroqarz</t>
         </is>
       </c>
       <c r="E398" s="3" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F398" s="3" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G398" s="3" t="inlineStr"/>
-      <c r="H398" s="3" t="inlineStr"/>
+      <c r="H398" s="3" t="inlineStr">
+        <is>
+          <t>6–36 oy</t>
+        </is>
+      </c>
       <c r="I398" s="3" t="inlineStr">
         <is>
-          <t>5 mlrd gacha</t>
+          <t>1–90 mln</t>
         </is>
       </c>
       <c r="J398" s="3" t="inlineStr">
@@ -25228,18 +25244,18 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L398" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M398" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L398" s="3" t="inlineStr"/>
+      <c r="M398" s="3" t="inlineStr">
+        <is>
+          <t>Kreditlar ro'yxatida '30% dan' deb ko'rsatilgan</t>
+        </is>
+      </c>
       <c r="N398" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/business/smelending/biznes-uskorennyj</t>
+          <t>https://tengebank.uz/en/credit/mikrozajm-onlajn</t>
         </is>
       </c>
     </row>
@@ -25251,24 +25267,24 @@
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>YaTT uchun onlayn kredit</t>
+          <t>Onlayn mikroqarz</t>
         </is>
       </c>
       <c r="E399" s="3" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="F399" s="3" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="G399" s="3" t="inlineStr"/>
       <c r="H399" s="3" t="inlineStr">
@@ -25278,7 +25294,7 @@
       </c>
       <c r="I399" s="3" t="inlineStr">
         <is>
-          <t>300 mln gacha</t>
+          <t>90 mln gacha</t>
         </is>
       </c>
       <c r="J399" s="3" t="inlineStr">
@@ -25299,44 +25315,44 @@
       <c r="M399" s="3" t="inlineStr"/>
       <c r="N399" s="6" t="inlineStr">
         <is>
-          <t>https://tengebank.uz/business/smelending/online-business</t>
+          <t>https://tengebank.uz/credit/mikrozajm-onlajn</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="3" t="inlineStr">
         <is>
-          <t>Trastbank</t>
+          <t>Tenge Bank</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Tezkor biznes</t>
         </is>
       </c>
       <c r="E400" s="3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F400" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G400" s="3" t="inlineStr"/>
-      <c r="H400" s="3" t="inlineStr">
-        <is>
-          <t>48–60 oy</t>
-        </is>
-      </c>
-      <c r="I400" s="3" t="inlineStr"/>
+      <c r="H400" s="3" t="inlineStr"/>
+      <c r="I400" s="3" t="inlineStr">
+        <is>
+          <t>5 mlrd gacha</t>
+        </is>
+      </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -25344,55 +25360,59 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L400" s="3" t="inlineStr"/>
-      <c r="M400" s="3" t="inlineStr">
-        <is>
-          <t>Bosh sahifa: 21% dan, 60 oy; maqola: 24% (30% badal) / 22% (50% badal), 48 oy</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L400" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M400" s="3" t="inlineStr"/>
       <c r="N400" s="6" t="inlineStr">
         <is>
-          <t>https://trustbank.uz/uz/private/</t>
+          <t>https://tengebank.uz/business/smelending/biznes-uskorennyj</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
         <is>
-          <t>Trastbank</t>
+          <t>Tenge Bank</t>
         </is>
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
-          <t>“Sharq bahori” ipoteka krediti</t>
+          <t>YaTT uchun onlayn kredit</t>
         </is>
       </c>
       <c r="E401" s="3" t="n">
-        <v>17</v>
+        <v>24.9</v>
       </c>
       <c r="F401" s="3" t="n">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="G401" s="3" t="inlineStr"/>
       <c r="H401" s="3" t="inlineStr">
         <is>
-          <t>20 yilgacha</t>
-        </is>
-      </c>
-      <c r="I401" s="3" t="inlineStr"/>
+          <t>3 yilgacha</t>
+        </is>
+      </c>
+      <c r="I401" s="3" t="inlineStr">
+        <is>
+          <t>300 mln gacha</t>
+        </is>
+      </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -25411,7 +25431,7 @@
       <c r="M401" s="3" t="inlineStr"/>
       <c r="N401" s="6" t="inlineStr">
         <is>
-          <t>https://trustbank.uz/uz/private/crediting/sharq-bahori-ipoteka-krediti/</t>
+          <t>https://tengebank.uz/business/smelending/online-business</t>
         </is>
       </c>
     </row>
@@ -25428,24 +25448,24 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>Bankning o‘z mablag‘lari hisobidan ajratiladigan ipoteka krediti</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="E402" s="3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F402" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G402" s="3" t="inlineStr"/>
       <c r="H402" s="3" t="inlineStr">
         <is>
-          <t>10 yilgacha</t>
+          <t>48–60 oy</t>
         </is>
       </c>
       <c r="I402" s="3" t="inlineStr"/>
@@ -25456,18 +25476,18 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L402" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M402" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L402" s="3" t="inlineStr"/>
+      <c r="M402" s="3" t="inlineStr">
+        <is>
+          <t>Bosh sahifa: 21% dan, 60 oy; maqola: 24% (30% badal) / 22% (50% badal), 48 oy</t>
+        </is>
+      </c>
       <c r="N402" s="6" t="inlineStr">
         <is>
-          <t>https://trustbank.uz/uz/private/crediting/bankning-o-z-mablag-lari-hisobidan-ajratiladigan-ipoteka-krediti/</t>
+          <t>https://trustbank.uz/uz/private/</t>
         </is>
       </c>
     </row>
@@ -25489,19 +25509,19 @@
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>Yillik foiz:</t>
+          <t>“Sharq bahori” ipoteka krediti</t>
         </is>
       </c>
       <c r="E403" s="3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F403" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G403" s="3" t="inlineStr"/>
       <c r="H403" s="3" t="inlineStr">
         <is>
-          <t>15 yilgacha</t>
+          <t>20 yilgacha</t>
         </is>
       </c>
       <c r="I403" s="3" t="inlineStr"/>
@@ -25523,7 +25543,7 @@
       <c r="M403" s="3" t="inlineStr"/>
       <c r="N403" s="6" t="inlineStr">
         <is>
-          <t>https://trustbank.uz/uz/private/crediting/birlamchi-va-ikkilamchi-bozordan-uy-joy-sotib-olish-uchun-ipoteka-krediti/</t>
+          <t>https://trustbank.uz/uz/private/crediting/sharq-bahori-ipoteka-krediti/</t>
         </is>
       </c>
     </row>
@@ -25545,19 +25565,19 @@
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Yillik foiz:</t>
+          <t>Bankning o‘z mablag‘lari hisobidan ajratiladigan ipoteka krediti</t>
         </is>
       </c>
       <c r="E404" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F404" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G404" s="3" t="inlineStr"/>
       <c r="H404" s="3" t="inlineStr">
         <is>
-          <t>20 yilgacha</t>
+          <t>10 yilgacha</t>
         </is>
       </c>
       <c r="I404" s="3" t="inlineStr"/>
@@ -25579,7 +25599,7 @@
       <c r="M404" s="3" t="inlineStr"/>
       <c r="N404" s="6" t="inlineStr">
         <is>
-          <t>https://trustbank.uz/uz/private/crediting/golden-house-property-group-qurilish-kompaniyasi-qoshidagi-korxonalar-tomonidan-qurilayotgan-uy-joy-/</t>
+          <t>https://trustbank.uz/uz/private/crediting/bankning-o-z-mablag-lari-hisobidan-ajratiladigan-ipoteka-krediti/</t>
         </is>
       </c>
     </row>
@@ -25601,19 +25621,19 @@
       </c>
       <c r="D405" s="3" t="inlineStr">
         <is>
-          <t>Birlamchi bozordan uy-joy (kvartira) sotib olish uchun ipoteka krediti</t>
+          <t>Yillik foiz:</t>
         </is>
       </c>
       <c r="E405" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F405" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G405" s="3" t="inlineStr"/>
       <c r="H405" s="3" t="inlineStr">
         <is>
-          <t>20 yilgacha</t>
+          <t>15 yilgacha</t>
         </is>
       </c>
       <c r="I405" s="3" t="inlineStr"/>
@@ -25635,7 +25655,7 @@
       <c r="M405" s="3" t="inlineStr"/>
       <c r="N405" s="6" t="inlineStr">
         <is>
-          <t>https://trustbank.uz/uz/private/crediting/birlamchi-bozordan-uy-sotib-olish-uchun-ipoteka-krediti/</t>
+          <t>https://trustbank.uz/uz/private/crediting/birlamchi-va-ikkilamchi-bozordan-uy-joy-sotib-olish-uchun-ipoteka-krediti/</t>
         </is>
       </c>
     </row>
@@ -25652,12 +25672,12 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>Yashil energiya</t>
+          <t>Yillik foiz:</t>
         </is>
       </c>
       <c r="E406" s="3" t="n">
@@ -25669,7 +25689,7 @@
       <c r="G406" s="3" t="inlineStr"/>
       <c r="H406" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>20 yilgacha</t>
         </is>
       </c>
       <c r="I406" s="3" t="inlineStr"/>
@@ -25691,7 +25711,7 @@
       <c r="M406" s="3" t="inlineStr"/>
       <c r="N406" s="6" t="inlineStr">
         <is>
-          <t>https://trustbank.uz/uz/private/crediting/quyosh-panellarini-sotib-olish-va-o-rnatish-uchun-kredit/</t>
+          <t>https://trustbank.uz/uz/private/crediting/golden-house-property-group-qurilish-kompaniyasi-qoshidagi-korxonalar-tomonidan-qurilayotgan-uy-joy-/</t>
         </is>
       </c>
     </row>
@@ -25708,24 +25728,24 @@
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>Kredit karta</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
         <is>
-          <t>"Overdraft" krediti</t>
+          <t>Birlamchi bozordan uy-joy (kvartira) sotib olish uchun ipoteka krediti</t>
         </is>
       </c>
       <c r="E407" s="3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F407" s="3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G407" s="3" t="inlineStr"/>
       <c r="H407" s="3" t="inlineStr">
         <is>
-          <t>1 yilgacha</t>
+          <t>20 yilgacha</t>
         </is>
       </c>
       <c r="I407" s="3" t="inlineStr"/>
@@ -25747,7 +25767,7 @@
       <c r="M407" s="3" t="inlineStr"/>
       <c r="N407" s="6" t="inlineStr">
         <is>
-          <t>https://trustbank.uz/uz/private/crediting/overdraft/</t>
+          <t>https://trustbank.uz/uz/private/crediting/birlamchi-bozordan-uy-sotib-olish-uchun-ipoteka-krediti/</t>
         </is>
       </c>
     </row>
@@ -25764,24 +25784,24 @@
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>Onlayn mikroqarz</t>
+          <t>Yashil energiya</t>
         </is>
       </c>
       <c r="E408" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F408" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G408" s="3" t="inlineStr"/>
       <c r="H408" s="3" t="inlineStr">
         <is>
-          <t>12 oygacha</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I408" s="3" t="inlineStr"/>
@@ -25792,14 +25812,18 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L408" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L408" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M408" s="3" t="inlineStr"/>
       <c r="N408" s="6" t="inlineStr">
         <is>
-          <t>https://trustbank.uz/uz/private/crediting/online-microloan/</t>
+          <t>https://trustbank.uz/uz/private/crediting/quyosh-panellarini-sotib-olish-va-o-rnatish-uchun-kredit/</t>
         </is>
       </c>
     </row>
@@ -25811,29 +25835,29 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Kredit karta</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>Lizing</t>
+          <t>"Overdraft" krediti</t>
         </is>
       </c>
       <c r="E409" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F409" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G409" s="3" t="inlineStr"/>
       <c r="H409" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 1 yil</t>
+          <t>1 yilgacha</t>
         </is>
       </c>
       <c r="I409" s="3" t="inlineStr"/>
@@ -25855,14 +25879,14 @@
       <c r="M409" s="3" t="inlineStr"/>
       <c r="N409" s="6" t="inlineStr">
         <is>
-          <t>https://trustbank.uz/uz/corporate/leasing/</t>
+          <t>https://trustbank.uz/uz/private/crediting/overdraft/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
         <is>
-          <t>Turonbank</t>
+          <t>Trastbank</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -25872,31 +25896,27 @@
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>“Green Avto” Avtokrediti</t>
+          <t>Onlayn mikroqarz</t>
         </is>
       </c>
       <c r="E410" s="3" t="n">
-        <v>20.99</v>
+        <v>25</v>
       </c>
       <c r="F410" s="3" t="n">
-        <v>28.9</v>
+        <v>25</v>
       </c>
       <c r="G410" s="3" t="inlineStr"/>
       <c r="H410" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 5 yil</t>
-        </is>
-      </c>
-      <c r="I410" s="3" t="inlineStr">
-        <is>
-          <t>20.286 ming – 824 mln</t>
-        </is>
-      </c>
+          <t>12 oygacha</t>
+        </is>
+      </c>
+      <c r="I410" s="3" t="inlineStr"/>
       <c r="J410" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -25904,59 +25924,51 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L410" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L410" s="3" t="inlineStr"/>
       <c r="M410" s="3" t="inlineStr"/>
       <c r="N410" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/private/crediting/avtokredit-ecogreencar/</t>
+          <t>https://trustbank.uz/uz/private/crediting/online-microloan/</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
         <is>
-          <t>Turonbank</t>
+          <t>Trastbank</t>
         </is>
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>“AvtoSelf 2.0” Avtokrediti</t>
+          <t>Lizing</t>
         </is>
       </c>
       <c r="E411" s="3" t="n">
-        <v>20.99</v>
+        <v>30</v>
       </c>
       <c r="F411" s="3" t="n">
-        <v>28.9</v>
+        <v>30</v>
       </c>
       <c r="G411" s="3" t="inlineStr"/>
       <c r="H411" s="3" t="inlineStr">
         <is>
-          <t>1 yil – 5 yil</t>
-        </is>
-      </c>
-      <c r="I411" s="3" t="inlineStr">
-        <is>
-          <t>22.817 ming – 494.4 mln</t>
-        </is>
-      </c>
+          <t>3 oy – 1 yil</t>
+        </is>
+      </c>
+      <c r="I411" s="3" t="inlineStr"/>
       <c r="J411" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -25975,7 +25987,7 @@
       <c r="M411" s="3" t="inlineStr"/>
       <c r="N411" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/private/crediting/avtokredit-avtoself/</t>
+          <t>https://trustbank.uz/uz/corporate/leasing/</t>
         </is>
       </c>
     </row>
@@ -25997,22 +26009,26 @@
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>Imkoniyat 2.0</t>
+          <t>“Green Avto” Avtokrediti</t>
         </is>
       </c>
       <c r="E412" s="3" t="n">
-        <v>25</v>
+        <v>20.99</v>
       </c>
       <c r="F412" s="3" t="n">
-        <v>25</v>
+        <v>28.9</v>
       </c>
       <c r="G412" s="3" t="inlineStr"/>
       <c r="H412" s="3" t="inlineStr">
         <is>
-          <t>5 yilgacha</t>
-        </is>
-      </c>
-      <c r="I412" s="3" t="inlineStr"/>
+          <t>1 oy – 5 yil</t>
+        </is>
+      </c>
+      <c r="I412" s="3" t="inlineStr">
+        <is>
+          <t>20.286 ming – 824 mln</t>
+        </is>
+      </c>
       <c r="J412" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -26020,18 +26036,18 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L412" s="3" t="inlineStr"/>
-      <c r="M412" s="3" t="inlineStr">
-        <is>
-          <t>Ayrim mijozlar uchun 0% avtokreditlar ham bor</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L412" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M412" s="3" t="inlineStr"/>
       <c r="N412" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/private/crediting/avtokredit-imkoniyat/</t>
+          <t>https://turonbank.uz/uz/private/crediting/avtokredit-ecogreencar/</t>
         </is>
       </c>
     </row>
@@ -26048,12 +26064,12 @@
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>Biznesim maqsadim</t>
+          <t>“AvtoSelf 2.0” Avtokrediti</t>
         </is>
       </c>
       <c r="E413" s="3" t="n">
@@ -26065,12 +26081,12 @@
       <c r="G413" s="3" t="inlineStr"/>
       <c r="H413" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 5 yil</t>
+          <t>1 yil – 5 yil</t>
         </is>
       </c>
       <c r="I413" s="3" t="inlineStr">
         <is>
-          <t>842.933 ming – 50 mln</t>
+          <t>22.817 ming – 494.4 mln</t>
         </is>
       </c>
       <c r="J413" s="3" t="inlineStr">
@@ -26091,7 +26107,7 @@
       <c r="M413" s="3" t="inlineStr"/>
       <c r="N413" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/private/crediting/biznesim-maqsadim/</t>
+          <t>https://turonbank.uz/uz/private/crediting/avtokredit-avtoself/</t>
         </is>
       </c>
     </row>
@@ -26108,24 +26124,24 @@
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka (Yanada oson)</t>
+          <t>Imkoniyat 2.0</t>
         </is>
       </c>
       <c r="E414" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F414" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G414" s="3" t="inlineStr"/>
       <c r="H414" s="3" t="inlineStr">
         <is>
-          <t>10 yilgacha</t>
+          <t>5 yilgacha</t>
         </is>
       </c>
       <c r="I414" s="3" t="inlineStr"/>
@@ -26140,10 +26156,14 @@
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
-      <c r="M414" s="3" t="inlineStr"/>
+      <c r="M414" s="3" t="inlineStr">
+        <is>
+          <t>Ayrim mijozlar uchun 0% avtokreditlar ham bor</t>
+        </is>
+      </c>
       <c r="N414" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/private/crediting/ipoteka-krediti-yagona-oson/</t>
+          <t>https://turonbank.uz/uz/private/crediting/avtokredit-imkoniyat/</t>
         </is>
       </c>
     </row>
@@ -26160,27 +26180,31 @@
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka krediti</t>
+          <t>Biznesim maqsadim</t>
         </is>
       </c>
       <c r="E415" s="3" t="n">
-        <v>20</v>
+        <v>20.99</v>
       </c>
       <c r="F415" s="3" t="n">
-        <v>20</v>
+        <v>28.9</v>
       </c>
       <c r="G415" s="3" t="inlineStr"/>
       <c r="H415" s="3" t="inlineStr">
         <is>
-          <t>20 yilgacha</t>
-        </is>
-      </c>
-      <c r="I415" s="3" t="inlineStr"/>
+          <t>1 oy – 5 yil</t>
+        </is>
+      </c>
+      <c r="I415" s="3" t="inlineStr">
+        <is>
+          <t>842.933 ming – 50 mln</t>
+        </is>
+      </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -26188,18 +26212,18 @@
       </c>
       <c r="K415" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L415" s="3" t="inlineStr"/>
-      <c r="M415" s="3" t="inlineStr">
-        <is>
-          <t>Boshlang'ich badal 26%</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L415" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M415" s="3" t="inlineStr"/>
       <c r="N415" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/private/crediting/ipoteka-krediti/</t>
+          <t>https://turonbank.uz/uz/private/crediting/biznesim-maqsadim/</t>
         </is>
       </c>
     </row>
@@ -26216,31 +26240,27 @@
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>Kredit haqida</t>
+          <t>Ipoteka (Yanada oson)</t>
         </is>
       </c>
       <c r="E416" s="3" t="n">
-        <v>28.9</v>
+        <v>26</v>
       </c>
       <c r="F416" s="3" t="n">
-        <v>28.9</v>
+        <v>26</v>
       </c>
       <c r="G416" s="3" t="inlineStr"/>
       <c r="H416" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 1 yil</t>
-        </is>
-      </c>
-      <c r="I416" s="3" t="inlineStr">
-        <is>
-          <t>10 mln gacha</t>
-        </is>
-      </c>
+          <t>10 yilgacha</t>
+        </is>
+      </c>
+      <c r="I416" s="3" t="inlineStr"/>
       <c r="J416" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -26248,18 +26268,14 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L416" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L416" s="3" t="inlineStr"/>
       <c r="M416" s="3" t="inlineStr"/>
       <c r="N416" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/upload/iblock/368/2em3p0hf1je11eqqnwzqyl277o5w8gbz/tarif_fiz_uz_12.05..xlsx</t>
+          <t>https://turonbank.uz/uz/private/crediting/ipoteka-krediti-yagona-oson/</t>
         </is>
       </c>
     </row>
@@ -26276,31 +26292,27 @@
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>Barakali limonzor</t>
+          <t>Ipoteka krediti</t>
         </is>
       </c>
       <c r="E417" s="3" t="n">
-        <v>20.99</v>
+        <v>20</v>
       </c>
       <c r="F417" s="3" t="n">
-        <v>28.9</v>
+        <v>20</v>
       </c>
       <c r="G417" s="3" t="inlineStr"/>
       <c r="H417" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 7 yil</t>
-        </is>
-      </c>
-      <c r="I417" s="3" t="inlineStr">
-        <is>
-          <t>23.4259 ming – 41.2 mln</t>
-        </is>
-      </c>
+          <t>20 yilgacha</t>
+        </is>
+      </c>
+      <c r="I417" s="3" t="inlineStr"/>
       <c r="J417" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -26308,18 +26320,18 @@
       </c>
       <c r="K417" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L417" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M417" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L417" s="3" t="inlineStr"/>
+      <c r="M417" s="3" t="inlineStr">
+        <is>
+          <t>Boshlang'ich badal 26%</t>
+        </is>
+      </c>
       <c r="N417" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/private/crediting/barakali-limonzor/</t>
+          <t>https://turonbank.uz/uz/private/crediting/ipoteka-krediti/</t>
         </is>
       </c>
     </row>
@@ -26336,29 +26348,29 @@
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>Kredit miqdori</t>
+          <t>Kredit haqida</t>
         </is>
       </c>
       <c r="E418" s="3" t="n">
-        <v>27.9</v>
+        <v>28.9</v>
       </c>
       <c r="F418" s="3" t="n">
-        <v>30.9</v>
+        <v>28.9</v>
       </c>
       <c r="G418" s="3" t="inlineStr"/>
       <c r="H418" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 4 yil</t>
+          <t>3 oy – 1 yil</t>
         </is>
       </c>
       <c r="I418" s="3" t="inlineStr">
         <is>
-          <t>1 mln – 100 mln</t>
+          <t>10 mln gacha</t>
         </is>
       </c>
       <c r="J418" s="3" t="inlineStr">
@@ -26379,7 +26391,7 @@
       <c r="M418" s="3" t="inlineStr"/>
       <c r="N418" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/private/crediting/mikroqarz/</t>
+          <t>https://turonbank.uz/upload/iblock/368/2em3p0hf1je11eqqnwzqyl277o5w8gbz/tarif_fiz_uz_12.05..xlsx</t>
         </is>
       </c>
     </row>
@@ -26396,12 +26408,12 @@
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
         <is>
-          <t>Mahalla loyihasi mikrokrediti</t>
+          <t>Barakali limonzor</t>
         </is>
       </c>
       <c r="E419" s="3" t="n">
@@ -26413,12 +26425,12 @@
       <c r="G419" s="3" t="inlineStr"/>
       <c r="H419" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 5 yil</t>
+          <t>1 oy – 7 yil</t>
         </is>
       </c>
       <c r="I419" s="3" t="inlineStr">
         <is>
-          <t>1 mln – 81.9771 mln</t>
+          <t>23.4259 ming – 41.2 mln</t>
         </is>
       </c>
       <c r="J419" s="3" t="inlineStr">
@@ -26439,7 +26451,7 @@
       <c r="M419" s="3" t="inlineStr"/>
       <c r="N419" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/private/crediting/mahalla-loyihasi-mikrokrediti/</t>
+          <t>https://turonbank.uz/uz/private/crediting/barakali-limonzor/</t>
         </is>
       </c>
     </row>
@@ -26451,34 +26463,34 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>Welcome krediti</t>
+          <t>Kredit miqdori</t>
         </is>
       </c>
       <c r="E420" s="3" t="n">
-        <v>27.99</v>
+        <v>27.9</v>
       </c>
       <c r="F420" s="3" t="n">
-        <v>27.99</v>
+        <v>30.9</v>
       </c>
       <c r="G420" s="3" t="inlineStr"/>
       <c r="H420" s="3" t="inlineStr">
         <is>
-          <t>36 oygacha</t>
+          <t>1 oy – 4 yil</t>
         </is>
       </c>
       <c r="I420" s="3" t="inlineStr">
         <is>
-          <t>50 mln gacha</t>
+          <t>1 mln – 100 mln</t>
         </is>
       </c>
       <c r="J420" s="3" t="inlineStr">
@@ -26488,14 +26500,18 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L420" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L420" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M420" s="3" t="inlineStr"/>
       <c r="N420" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/corporate/crediting/welcome-krediti/</t>
+          <t>https://turonbank.uz/uz/private/crediting/mikroqarz/</t>
         </is>
       </c>
     </row>
@@ -26507,32 +26523,36 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
         <is>
-          <t>Mikrokreditlash</t>
+          <t>Mahalla loyihasi mikrokrediti</t>
         </is>
       </c>
       <c r="E421" s="3" t="n">
-        <v>27.99</v>
+        <v>20.99</v>
       </c>
       <c r="F421" s="3" t="n">
-        <v>27.99</v>
+        <v>28.9</v>
       </c>
       <c r="G421" s="3" t="inlineStr"/>
       <c r="H421" s="3" t="inlineStr">
         <is>
-          <t>36 oygacha</t>
-        </is>
-      </c>
-      <c r="I421" s="3" t="inlineStr"/>
+          <t>1 oy – 5 yil</t>
+        </is>
+      </c>
+      <c r="I421" s="3" t="inlineStr">
+        <is>
+          <t>1 mln – 81.9771 mln</t>
+        </is>
+      </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -26540,14 +26560,18 @@
       </c>
       <c r="K421" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L421" s="3" t="inlineStr"/>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L421" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M421" s="3" t="inlineStr"/>
       <c r="N421" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/corporate/crediting/microcredit9237/</t>
+          <t>https://turonbank.uz/uz/private/crediting/mahalla-loyihasi-mikrokrediti/</t>
         </is>
       </c>
     </row>
@@ -26569,7 +26593,7 @@
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>Investitsion kredit</t>
+          <t>Welcome krediti</t>
         </is>
       </c>
       <c r="E422" s="3" t="n">
@@ -26581,10 +26605,14 @@
       <c r="G422" s="3" t="inlineStr"/>
       <c r="H422" s="3" t="inlineStr">
         <is>
-          <t>36–84 oy</t>
-        </is>
-      </c>
-      <c r="I422" s="3" t="inlineStr"/>
+          <t>36 oygacha</t>
+        </is>
+      </c>
+      <c r="I422" s="3" t="inlineStr">
+        <is>
+          <t>50 mln gacha</t>
+        </is>
+      </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -26599,41 +26627,41 @@
       <c r="M422" s="3" t="inlineStr"/>
       <c r="N422" s="6" t="inlineStr">
         <is>
-          <t>https://turonbank.uz/uz/corporate/crediting/investment-loan/</t>
+          <t>https://turonbank.uz/uz/corporate/crediting/welcome-krediti/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
         <is>
-          <t>Universal bank</t>
+          <t>Turonbank</t>
         </is>
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
         <is>
-          <t>Comfortable (yangi avtomobil)</t>
+          <t>Mikrokreditlash</t>
         </is>
       </c>
       <c r="E423" s="3" t="n">
-        <v>30</v>
+        <v>27.99</v>
       </c>
       <c r="F423" s="3" t="n">
-        <v>34</v>
+        <v>27.99</v>
       </c>
       <c r="G423" s="3" t="inlineStr"/>
       <c r="H423" s="3" t="inlineStr">
         <is>
-          <t>36–60 oy</t>
+          <t>36 oygacha</t>
         </is>
       </c>
       <c r="I423" s="3" t="inlineStr"/>
@@ -26648,52 +26676,44 @@
         </is>
       </c>
       <c r="L423" s="3" t="inlineStr"/>
-      <c r="M423" s="3" t="inlineStr">
-        <is>
-          <t>36 oy 30–32%, 60 oy 32–34%; 3 oygacha imtiyoz</t>
-        </is>
-      </c>
+      <c r="M423" s="3" t="inlineStr"/>
       <c r="N423" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/avtokredit-comfortable</t>
+          <t>https://turonbank.uz/uz/corporate/crediting/microcredit9237/</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
         <is>
-          <t>Universal bank</t>
+          <t>Turonbank</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>Avtokredit</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>Ikkilamchi bozor uchun</t>
+          <t>Investitsion kredit</t>
         </is>
       </c>
       <c r="E424" s="3" t="n">
-        <v>27</v>
+        <v>27.99</v>
       </c>
       <c r="F424" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="G424" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+        <v>27.99</v>
+      </c>
+      <c r="G424" s="3" t="inlineStr"/>
       <c r="H424" s="3" t="inlineStr">
         <is>
-          <t>36 oy</t>
+          <t>36–84 oy</t>
         </is>
       </c>
       <c r="I424" s="3" t="inlineStr"/>
@@ -26708,14 +26728,10 @@
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
-      <c r="M424" s="3" t="inlineStr">
-        <is>
-          <t>Boshlang'ich badal 36% dan</t>
-        </is>
-      </c>
+      <c r="M424" s="3" t="inlineStr"/>
       <c r="N424" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/avtokredit-ikkilamchi-bozor-uc</t>
+          <t>https://turonbank.uz/uz/corporate/crediting/investment-loan/</t>
         </is>
       </c>
     </row>
@@ -26732,31 +26748,27 @@
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
         <is>
-          <t>Biznesga birinchi qadam – “Lux”</t>
+          <t>Comfortable (yangi avtomobil)</t>
         </is>
       </c>
       <c r="E425" s="3" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F425" s="3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G425" s="3" t="inlineStr"/>
       <c r="H425" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 3 yil</t>
-        </is>
-      </c>
-      <c r="I425" s="3" t="inlineStr">
-        <is>
-          <t>45.804 – 100 mln</t>
-        </is>
-      </c>
+          <t>36–60 oy</t>
+        </is>
+      </c>
+      <c r="I425" s="3" t="inlineStr"/>
       <c r="J425" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -26764,18 +26776,18 @@
       </c>
       <c r="K425" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L425" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M425" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L425" s="3" t="inlineStr"/>
+      <c r="M425" s="3" t="inlineStr">
+        <is>
+          <t>36 oy 30–32%, 60 oy 32–34%; 3 oygacha imtiyoz</t>
+        </is>
+      </c>
       <c r="N425" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/biznesga-birinchi-qadam-lux</t>
+          <t>https://universalbank.uz/credit/avtokredit-comfortable</t>
         </is>
       </c>
     </row>
@@ -26792,31 +26804,31 @@
       </c>
       <c r="C426" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Avtokredit</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>Biznesga birinchi qadam – “Premium”</t>
+          <t>Ikkilamchi bozor uchun</t>
         </is>
       </c>
       <c r="E426" s="3" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F426" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="G426" s="3" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="G426" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="H426" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 3 yil</t>
-        </is>
-      </c>
-      <c r="I426" s="3" t="inlineStr">
-        <is>
-          <t>45.804 – 30 mln</t>
-        </is>
-      </c>
+          <t>36 oy</t>
+        </is>
+      </c>
+      <c r="I426" s="3" t="inlineStr"/>
       <c r="J426" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -26824,18 +26836,18 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L426" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M426" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L426" s="3" t="inlineStr"/>
+      <c r="M426" s="3" t="inlineStr">
+        <is>
+          <t>Boshlang'ich badal 36% dan</t>
+        </is>
+      </c>
       <c r="N426" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/biznesga-birinchi-qadam-premiu</t>
+          <t>https://universalbank.uz/credit/avtokredit-ikkilamchi-bozor-uc</t>
         </is>
       </c>
     </row>
@@ -26857,24 +26869,24 @@
       </c>
       <c r="D427" s="3" t="inlineStr">
         <is>
-          <t>Biznesga birinchi qadam – “Standart”</t>
+          <t>Biznesga birinchi qadam – “Lux”</t>
         </is>
       </c>
       <c r="E427" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F427" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G427" s="3" t="inlineStr"/>
       <c r="H427" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 2 yil</t>
+          <t>1 oy – 3 yil</t>
         </is>
       </c>
       <c r="I427" s="3" t="inlineStr">
         <is>
-          <t>57.992 – 20 mln</t>
+          <t>45.804 – 100 mln</t>
         </is>
       </c>
       <c r="J427" s="3" t="inlineStr">
@@ -26895,7 +26907,7 @@
       <c r="M427" s="3" t="inlineStr"/>
       <c r="N427" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/biznesga-birinchi-qadam-standa</t>
+          <t>https://universalbank.uz/credit/biznesga-birinchi-qadam-lux</t>
         </is>
       </c>
     </row>
@@ -26917,24 +26929,24 @@
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>Biznesga birinchi qadam – “Econom”</t>
+          <t>Biznesga birinchi qadam – “Premium”</t>
         </is>
       </c>
       <c r="E428" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F428" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G428" s="3" t="inlineStr"/>
       <c r="H428" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 1 yil</t>
+          <t>1 oy – 3 yil</t>
         </is>
       </c>
       <c r="I428" s="3" t="inlineStr">
         <is>
-          <t>98.474 – 10 mln</t>
+          <t>45.804 – 30 mln</t>
         </is>
       </c>
       <c r="J428" s="3" t="inlineStr">
@@ -26955,7 +26967,7 @@
       <c r="M428" s="3" t="inlineStr"/>
       <c r="N428" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/biznesga-birinchi-qadam-econom</t>
+          <t>https://universalbank.uz/credit/biznesga-birinchi-qadam-premiu</t>
         </is>
       </c>
     </row>
@@ -26972,27 +26984,31 @@
       </c>
       <c r="C429" s="3" t="inlineStr">
         <is>
-          <t>Ipoteka</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
         <is>
-          <t>Ipotekani qayta moliyalashtirish</t>
+          <t>Biznesga birinchi qadam – “Standart”</t>
         </is>
       </c>
       <c r="E429" s="3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F429" s="3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G429" s="3" t="inlineStr"/>
       <c r="H429" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 10 yil</t>
-        </is>
-      </c>
-      <c r="I429" s="3" t="inlineStr"/>
+          <t>1 oy – 2 yil</t>
+        </is>
+      </c>
+      <c r="I429" s="3" t="inlineStr">
+        <is>
+          <t>57.992 – 20 mln</t>
+        </is>
+      </c>
       <c r="J429" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -27011,7 +27027,7 @@
       <c r="M429" s="3" t="inlineStr"/>
       <c r="N429" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/ipotekani-qayta-moliyalashtiri</t>
+          <t>https://universalbank.uz/credit/biznesga-birinchi-qadam-standa</t>
         </is>
       </c>
     </row>
@@ -27028,33 +27044,29 @@
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol krediti</t>
+          <t>Biznesga birinchi qadam – “Econom”</t>
         </is>
       </c>
       <c r="E430" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F430" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G430" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="G430" s="3" t="inlineStr"/>
       <c r="H430" s="3" t="inlineStr">
         <is>
-          <t>36 oygacha</t>
+          <t>1 oy – 1 yil</t>
         </is>
       </c>
       <c r="I430" s="3" t="inlineStr">
         <is>
-          <t>200 BHM gacha</t>
+          <t>98.474 – 10 mln</t>
         </is>
       </c>
       <c r="J430" s="3" t="inlineStr">
@@ -27064,18 +27076,18 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L430" s="3" t="inlineStr"/>
-      <c r="M430" s="3" t="inlineStr">
-        <is>
-          <t>Byudjet xodimlari uchun 30%</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L430" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M430" s="3" t="inlineStr"/>
       <c r="N430" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/iste'mol-krediti</t>
+          <t>https://universalbank.uz/credit/biznesga-birinchi-qadam-econom</t>
         </is>
       </c>
     </row>
@@ -27092,24 +27104,24 @@
       </c>
       <c r="C431" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Ipoteka</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
         <is>
-          <t>ISHONCH</t>
+          <t>Ipotekani qayta moliyalashtirish</t>
         </is>
       </c>
       <c r="E431" s="3" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F431" s="3" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G431" s="3" t="inlineStr"/>
       <c r="H431" s="3" t="inlineStr">
         <is>
-          <t>36 oygacha</t>
+          <t>3 oy – 10 yil</t>
         </is>
       </c>
       <c r="I431" s="3" t="inlineStr"/>
@@ -27120,18 +27132,18 @@
       </c>
       <c r="K431" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L431" s="3" t="inlineStr"/>
-      <c r="M431" s="3" t="inlineStr">
-        <is>
-          <t>1 oygacha imtiyoz</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L431" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M431" s="3" t="inlineStr"/>
       <c r="N431" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/mikroqarz-ishonch</t>
+          <t>https://universalbank.uz/credit/ipotekani-qayta-moliyalashtiri</t>
         </is>
       </c>
     </row>
@@ -27148,29 +27160,33 @@
       </c>
       <c r="C432" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz (byudjet)</t>
+          <t>Iste'mol krediti</t>
         </is>
       </c>
       <c r="E432" s="3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F432" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="G432" s="3" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="G432" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="H432" s="3" t="inlineStr">
         <is>
-          <t>12 oygacha</t>
+          <t>36 oygacha</t>
         </is>
       </c>
       <c r="I432" s="3" t="inlineStr">
         <is>
-          <t>50 mln gacha</t>
+          <t>200 BHM gacha</t>
         </is>
       </c>
       <c r="J432" s="3" t="inlineStr">
@@ -27186,12 +27202,12 @@
       <c r="L432" s="3" t="inlineStr"/>
       <c r="M432" s="3" t="inlineStr">
         <is>
-          <t>6 oygacha 24%, 6–12 oy 26%</t>
+          <t>Byudjet xodimlari uchun 30%</t>
         </is>
       </c>
       <c r="N432" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/mikroqarz-byudjet</t>
+          <t>https://universalbank.uz/credit/iste'mol-krediti</t>
         </is>
       </c>
     </row>
@@ -27213,26 +27229,22 @@
       </c>
       <c r="D433" s="3" t="inlineStr">
         <is>
-          <t>Mikrokredit - 300</t>
+          <t>ISHONCH</t>
         </is>
       </c>
       <c r="E433" s="3" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G433" s="3" t="inlineStr"/>
       <c r="H433" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 5 yil</t>
-        </is>
-      </c>
-      <c r="I433" s="3" t="inlineStr">
-        <is>
-          <t>300 mln gacha</t>
-        </is>
-      </c>
+          <t>36 oygacha</t>
+        </is>
+      </c>
+      <c r="I433" s="3" t="inlineStr"/>
       <c r="J433" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -27240,18 +27252,18 @@
       </c>
       <c r="K433" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L433" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M433" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L433" s="3" t="inlineStr"/>
+      <c r="M433" s="3" t="inlineStr">
+        <is>
+          <t>1 oygacha imtiyoz</t>
+        </is>
+      </c>
       <c r="N433" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/mikrokredit-300</t>
+          <t>https://universalbank.uz/credit/mikroqarz-ishonch</t>
         </is>
       </c>
     </row>
@@ -27273,24 +27285,24 @@
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Mikroqarz (byudjet)</t>
         </is>
       </c>
       <c r="E434" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F434" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G434" s="3" t="inlineStr"/>
       <c r="H434" s="3" t="inlineStr">
         <is>
-          <t>3 yil – 5 yil</t>
+          <t>12 oygacha</t>
         </is>
       </c>
       <c r="I434" s="3" t="inlineStr">
         <is>
-          <t>100 mln gacha</t>
+          <t>50 mln gacha</t>
         </is>
       </c>
       <c r="J434" s="3" t="inlineStr">
@@ -27300,18 +27312,18 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L434" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M434" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L434" s="3" t="inlineStr"/>
+      <c r="M434" s="3" t="inlineStr">
+        <is>
+          <t>6 oygacha 24%, 6–12 oy 26%</t>
+        </is>
+      </c>
       <c r="N434" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/credit/mikroqarz</t>
+          <t>https://universalbank.uz/credit/mikroqarz-byudjet</t>
         </is>
       </c>
     </row>
@@ -27323,32 +27335,36 @@
       </c>
       <c r="B435" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C435" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D435" s="3" t="inlineStr">
         <is>
-          <t>Biznes kreditlari</t>
+          <t>Mikrokredit - 300</t>
         </is>
       </c>
       <c r="E435" s="3" t="n">
         <v>26</v>
       </c>
       <c r="F435" s="3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G435" s="3" t="inlineStr"/>
       <c r="H435" s="3" t="inlineStr">
         <is>
-          <t>36–120 oy</t>
-        </is>
-      </c>
-      <c r="I435" s="3" t="inlineStr"/>
+          <t>1 oy – 5 yil</t>
+        </is>
+      </c>
+      <c r="I435" s="3" t="inlineStr">
+        <is>
+          <t>300 mln gacha</t>
+        </is>
+      </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -27356,18 +27372,18 @@
       </c>
       <c r="K435" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L435" s="3" t="inlineStr"/>
-      <c r="M435" s="3" t="inlineStr">
-        <is>
-          <t>USD da 12–14%</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L435" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M435" s="3" t="inlineStr"/>
       <c r="N435" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/juristic/kreditlar</t>
+          <t>https://universalbank.uz/credit/mikrokredit-300</t>
         </is>
       </c>
     </row>
@@ -27379,32 +27395,36 @@
       </c>
       <c r="B436" s="3" t="inlineStr">
         <is>
-          <t>Yuridik</t>
+          <t>Jismoniy</t>
         </is>
       </c>
       <c r="C436" s="3" t="inlineStr">
         <is>
-          <t>Biznes</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>Good customer 100</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="E436" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F436" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G436" s="3" t="inlineStr"/>
       <c r="H436" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 3 yil</t>
-        </is>
-      </c>
-      <c r="I436" s="3" t="inlineStr"/>
+          <t>3 yil – 5 yil</t>
+        </is>
+      </c>
+      <c r="I436" s="3" t="inlineStr">
+        <is>
+          <t>100 mln gacha</t>
+        </is>
+      </c>
       <c r="J436" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -27423,7 +27443,7 @@
       <c r="M436" s="3" t="inlineStr"/>
       <c r="N436" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/juristic/credit/good-customer-100</t>
+          <t>https://universalbank.uz/credit/mikroqarz</t>
         </is>
       </c>
     </row>
@@ -27445,11 +27465,11 @@
       </c>
       <c r="D437" s="3" t="inlineStr">
         <is>
-          <t>Good customer 300</t>
+          <t>Biznes kreditlari</t>
         </is>
       </c>
       <c r="E437" s="3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F437" s="3" t="n">
         <v>30</v>
@@ -27457,7 +27477,7 @@
       <c r="G437" s="3" t="inlineStr"/>
       <c r="H437" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 3 yil</t>
+          <t>36–120 oy</t>
         </is>
       </c>
       <c r="I437" s="3" t="inlineStr"/>
@@ -27468,18 +27488,18 @@
       </c>
       <c r="K437" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
-        </is>
-      </c>
-      <c r="L437" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M437" s="3" t="inlineStr"/>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L437" s="3" t="inlineStr"/>
+      <c r="M437" s="3" t="inlineStr">
+        <is>
+          <t>USD da 12–14%</t>
+        </is>
+      </c>
       <c r="N437" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/juristic/credit/good-customer-300</t>
+          <t>https://universalbank.uz/juristic/kreditlar</t>
         </is>
       </c>
     </row>
@@ -27501,7 +27521,7 @@
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>Good customer 500</t>
+          <t>Good customer 100</t>
         </is>
       </c>
       <c r="E438" s="3" t="n">
@@ -27535,7 +27555,7 @@
       <c r="M438" s="3" t="inlineStr"/>
       <c r="N438" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/juristic/credit/good-customer-500</t>
+          <t>https://universalbank.uz/juristic/credit/good-customer-100</t>
         </is>
       </c>
     </row>
@@ -27557,11 +27577,11 @@
       </c>
       <c r="D439" s="3" t="inlineStr">
         <is>
-          <t>BlueOrchard</t>
+          <t>Good customer 300</t>
         </is>
       </c>
       <c r="E439" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F439" s="3" t="n">
         <v>30</v>
@@ -27569,7 +27589,7 @@
       <c r="G439" s="3" t="inlineStr"/>
       <c r="H439" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 5 yil</t>
+          <t>3 oy – 3 yil</t>
         </is>
       </c>
       <c r="I439" s="3" t="inlineStr"/>
@@ -27591,7 +27611,7 @@
       <c r="M439" s="3" t="inlineStr"/>
       <c r="N439" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/juristic/credit/blueorchard</t>
+          <t>https://universalbank.uz/juristic/credit/good-customer-300</t>
         </is>
       </c>
     </row>
@@ -27613,11 +27633,11 @@
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>Simbiotics</t>
+          <t>Good customer 500</t>
         </is>
       </c>
       <c r="E440" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F440" s="3" t="n">
         <v>30</v>
@@ -27625,7 +27645,7 @@
       <c r="G440" s="3" t="inlineStr"/>
       <c r="H440" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 5 yil</t>
+          <t>3 oy – 3 yil</t>
         </is>
       </c>
       <c r="I440" s="3" t="inlineStr"/>
@@ -27647,7 +27667,7 @@
       <c r="M440" s="3" t="inlineStr"/>
       <c r="N440" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/juristic/credit/simbiotics</t>
+          <t>https://universalbank.uz/juristic/credit/good-customer-500</t>
         </is>
       </c>
     </row>
@@ -27669,26 +27689,22 @@
       </c>
       <c r="D441" s="3" t="inlineStr">
         <is>
-          <t>Qulay</t>
+          <t>BlueOrchard</t>
         </is>
       </c>
       <c r="E441" s="3" t="n">
         <v>28</v>
       </c>
       <c r="F441" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G441" s="3" t="inlineStr"/>
       <c r="H441" s="3" t="inlineStr">
         <is>
-          <t>3 oy – 3 yil</t>
-        </is>
-      </c>
-      <c r="I441" s="3" t="inlineStr">
-        <is>
-          <t>3 mlrd gacha</t>
-        </is>
-      </c>
+          <t>6 oy – 5 yil</t>
+        </is>
+      </c>
+      <c r="I441" s="3" t="inlineStr"/>
       <c r="J441" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -27707,7 +27723,7 @@
       <c r="M441" s="3" t="inlineStr"/>
       <c r="N441" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/juristic/credit/qulay</t>
+          <t>https://universalbank.uz/juristic/credit/blueorchard</t>
         </is>
       </c>
     </row>
@@ -27729,14 +27745,14 @@
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>ESG Finance</t>
+          <t>Simbiotics</t>
         </is>
       </c>
       <c r="E442" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F442" s="3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G442" s="3" t="inlineStr"/>
       <c r="H442" s="3" t="inlineStr">
@@ -27744,11 +27760,7 @@
           <t>6 oy – 5 yil</t>
         </is>
       </c>
-      <c r="I442" s="3" t="inlineStr">
-        <is>
-          <t>3 mlrd gacha</t>
-        </is>
-      </c>
+      <c r="I442" s="3" t="inlineStr"/>
       <c r="J442" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -27767,46 +27779,46 @@
       <c r="M442" s="3" t="inlineStr"/>
       <c r="N442" s="6" t="inlineStr">
         <is>
-          <t>https://universalbank.uz/juristic/credit/esg-finance</t>
+          <t>https://universalbank.uz/juristic/credit/simbiotics</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
         <is>
-          <t>Uzum Bank</t>
+          <t>Universal bank</t>
         </is>
       </c>
       <c r="B443" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C443" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D443" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz (Uzum Nasiya orqali)</t>
+          <t>Qulay</t>
         </is>
       </c>
       <c r="E443" s="3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F443" s="3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G443" s="3" t="inlineStr"/>
       <c r="H443" s="3" t="inlineStr">
         <is>
-          <t>30 kun</t>
+          <t>3 oy – 3 yil</t>
         </is>
       </c>
       <c r="I443" s="3" t="inlineStr">
         <is>
-          <t>25 mln gacha</t>
+          <t>3 mlrd gacha</t>
         </is>
       </c>
       <c r="J443" s="3" t="inlineStr">
@@ -27816,55 +27828,59 @@
       </c>
       <c r="K443" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L443" s="3" t="inlineStr"/>
-      <c r="M443" s="3" t="inlineStr">
-        <is>
-          <t>30 kundan keyin qarz 12 ta to'lovga bo'linadi (Uzum Nasiya komissiyasi bilan); kartaga o'tkazish 5%</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L443" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M443" s="3" t="inlineStr"/>
       <c r="N443" s="6" t="inlineStr">
         <is>
-          <t>https://uzumbank.uz/en/card/</t>
+          <t>https://universalbank.uz/juristic/credit/qulay</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
         <is>
-          <t>Xalq banki</t>
+          <t>Universal bank</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
         <is>
-          <t>Jismoniy</t>
+          <t>Yuridik</t>
         </is>
       </c>
       <c r="C444" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Biznes</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>Byudjet tashkiloti xodimlari uchun</t>
+          <t>ESG Finance</t>
         </is>
       </c>
       <c r="E444" s="3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F444" s="3" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G444" s="3" t="inlineStr"/>
       <c r="H444" s="3" t="inlineStr">
         <is>
-          <t>4 yilgacha</t>
-        </is>
-      </c>
-      <c r="I444" s="3" t="inlineStr"/>
+          <t>6 oy – 5 yil</t>
+        </is>
+      </c>
+      <c r="I444" s="3" t="inlineStr">
+        <is>
+          <t>3 mlrd gacha</t>
+        </is>
+      </c>
       <c r="J444" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -27872,29 +27888,25 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
+          <t>Saytdan avtomatik</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr">
         <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="M444" s="3" t="inlineStr">
-        <is>
-          <t>2024 yilgi hujjat</t>
-        </is>
-      </c>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M444" s="3" t="inlineStr"/>
       <c r="N444" s="6" t="inlineStr">
         <is>
-          <t>https://xb.uz/cdn/2/uploads/2024/03/13/10/37/xFOk3qk78QLp4M9iml5Dtfxdpf4RAJg9WlWzWtIymDeLH1KET7RIL94TKXcXfUC7.pdf</t>
+          <t>https://universalbank.uz/juristic/credit/esg-finance</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
         <is>
-          <t>Xalq banki</t>
+          <t>Uzum Bank</t>
         </is>
       </c>
       <c r="B445" s="3" t="inlineStr">
@@ -27904,27 +27916,31 @@
       </c>
       <c r="C445" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol</t>
+          <t>Mikroqarz</t>
         </is>
       </c>
       <c r="D445" s="3" t="inlineStr">
         <is>
-          <t>Ish haqi loyihasi ishtirokchilari uchun</t>
+          <t>Mikroqarz (Uzum Nasiya orqali)</t>
         </is>
       </c>
       <c r="E445" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F445" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G445" s="3" t="inlineStr"/>
       <c r="H445" s="3" t="inlineStr">
         <is>
-          <t>1–4 yil</t>
-        </is>
-      </c>
-      <c r="I445" s="3" t="inlineStr"/>
+          <t>30 kun</t>
+        </is>
+      </c>
+      <c r="I445" s="3" t="inlineStr">
+        <is>
+          <t>25 mln gacha</t>
+        </is>
+      </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -27935,19 +27951,15 @@
           <t>Qo'lda tekshirilgan</t>
         </is>
       </c>
-      <c r="L445" s="3" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
+      <c r="L445" s="3" t="inlineStr"/>
       <c r="M445" s="3" t="inlineStr">
         <is>
-          <t>1 yil 25%, 2 yil 26%, 3 yil 28%, 4 yil 30%; 2024 yilgi hujjat</t>
+          <t>30 kundan keyin qarz 12 ta to'lovga bo'linadi (Uzum Nasiya komissiyasi bilan); kartaga o'tkazish 5%</t>
         </is>
       </c>
       <c r="N445" s="6" t="inlineStr">
         <is>
-          <t>https://xb.uz/cdn/2/uploads/2024/03/13/10/37/xFOk3qk78QLp4M9iml5Dtfxdpf4RAJg9WlWzWtIymDeLH1KET7RIL94TKXcXfUC7.pdf</t>
+          <t>https://uzumbank.uz/en/card/</t>
         </is>
       </c>
     </row>
@@ -27969,19 +27981,19 @@
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>"Moliyaviy ommabop" krediti</t>
+          <t>Byudjet tashkiloti xodimlari uchun</t>
         </is>
       </c>
       <c r="E446" s="3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F446" s="3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G446" s="3" t="inlineStr"/>
       <c r="H446" s="3" t="inlineStr">
         <is>
-          <t>3 yilgacha</t>
+          <t>4 yilgacha</t>
         </is>
       </c>
       <c r="I446" s="3" t="inlineStr"/>
@@ -27992,25 +28004,29 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
+          <t>Qo'lda tekshirilgan</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M446" s="3" t="inlineStr"/>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="M446" s="3" t="inlineStr">
+        <is>
+          <t>2024 yilgi hujjat</t>
+        </is>
+      </c>
       <c r="N446" s="6" t="inlineStr">
         <is>
-          <t>https://xb.uz/page/moliyaviy-ommabop-krediti</t>
+          <t>https://xb.uz/cdn/2/uploads/2024/03/13/10/37/xFOk3qk78QLp4M9iml5Dtfxdpf4RAJg9WlWzWtIymDeLH1KET7RIL94TKXcXfUC7.pdf</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
         <is>
-          <t>Ziraat Bank O'zbekiston</t>
+          <t>Xalq banki</t>
         </is>
       </c>
       <c r="B447" s="3" t="inlineStr">
@@ -28025,19 +28041,19 @@
       </c>
       <c r="D447" s="3" t="inlineStr">
         <is>
-          <t>Iste`mol kredit "Shinam uy"</t>
+          <t>Ish haqi loyihasi ishtirokchilari uchun</t>
         </is>
       </c>
       <c r="E447" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F447" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G447" s="3" t="inlineStr"/>
       <c r="H447" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 3 yil</t>
+          <t>1–4 yil</t>
         </is>
       </c>
       <c r="I447" s="3" t="inlineStr"/>
@@ -28048,25 +28064,29 @@
       </c>
       <c r="K447" s="3" t="inlineStr">
         <is>
-          <t>Saytdan avtomatik</t>
+          <t>Qo'lda tekshirilgan</t>
         </is>
       </c>
       <c r="L447" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M447" s="3" t="inlineStr"/>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="M447" s="3" t="inlineStr">
+        <is>
+          <t>1 yil 25%, 2 yil 26%, 3 yil 28%, 4 yil 30%; 2024 yilgi hujjat</t>
+        </is>
+      </c>
       <c r="N447" s="6" t="inlineStr">
         <is>
-          <t>https://ziraatbank.uz/uz/%D1%88%D0%B8%D0%BD%D0%B0%D0%BC-%D1%83%D0%B9</t>
+          <t>https://xb.uz/cdn/2/uploads/2024/03/13/10/37/xFOk3qk78QLp4M9iml5Dtfxdpf4RAJg9WlWzWtIymDeLH1KET7RIL94TKXcXfUC7.pdf</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
         <is>
-          <t>Ziraat Bank O'zbekiston</t>
+          <t>Xalq banki</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
@@ -28081,19 +28101,19 @@
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>Iste'mol kredit "Yashil Komfort"</t>
+          <t>"Moliyaviy ommabop" krediti</t>
         </is>
       </c>
       <c r="E448" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F448" s="3" t="n">
         <v>24</v>
-      </c>
-      <c r="F448" s="3" t="n">
-        <v>25</v>
       </c>
       <c r="G448" s="3" t="inlineStr"/>
       <c r="H448" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 5 yil</t>
+          <t>3 yilgacha</t>
         </is>
       </c>
       <c r="I448" s="3" t="inlineStr"/>
@@ -28115,7 +28135,7 @@
       <c r="M448" s="3" t="inlineStr"/>
       <c r="N448" s="6" t="inlineStr">
         <is>
-          <t>https://ziraatbank.uz/uz/iste-mol-kredit----yashil-komfort---</t>
+          <t>https://xb.uz/page/moliyaviy-ommabop-krediti</t>
         </is>
       </c>
     </row>
@@ -28137,19 +28157,19 @@
       </c>
       <c r="D449" s="3" t="inlineStr">
         <is>
-          <t>ECO SARMOYA</t>
+          <t>Iste`mol kredit "Shinam uy"</t>
         </is>
       </c>
       <c r="E449" s="3" t="n">
-        <v>23.5</v>
+        <v>25</v>
       </c>
       <c r="F449" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G449" s="3" t="inlineStr"/>
       <c r="H449" s="3" t="inlineStr">
         <is>
-          <t>6 oy – 5 yil</t>
+          <t>1 oy – 3 yil</t>
         </is>
       </c>
       <c r="I449" s="3" t="inlineStr"/>
@@ -28171,7 +28191,7 @@
       <c r="M449" s="3" t="inlineStr"/>
       <c r="N449" s="6" t="inlineStr">
         <is>
-          <t>https://ziraatbank.uz/uz/eco-sarmoya</t>
+          <t>https://ziraatbank.uz/uz/%D1%88%D0%B8%D0%BD%D0%B0%D0%BC-%D1%83%D0%B9</t>
         </is>
       </c>
     </row>
@@ -28188,31 +28208,27 @@
       </c>
       <c r="C450" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol kredit "Yashil Komfort"</t>
         </is>
       </c>
       <c r="E450" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F450" s="3" t="n">
         <v>25</v>
-      </c>
-      <c r="F450" s="3" t="n">
-        <v>26.5</v>
       </c>
       <c r="G450" s="3" t="inlineStr"/>
       <c r="H450" s="3" t="inlineStr">
         <is>
-          <t>1–36 oy</t>
-        </is>
-      </c>
-      <c r="I450" s="3" t="inlineStr">
-        <is>
-          <t>20 mln dan</t>
-        </is>
-      </c>
+          <t>6 oy – 5 yil</t>
+        </is>
+      </c>
+      <c r="I450" s="3" t="inlineStr"/>
       <c r="J450" s="3" t="inlineStr">
         <is>
           <t>UZS</t>
@@ -28220,18 +28236,18 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>Qo'lda tekshirilgan</t>
-        </is>
-      </c>
-      <c r="L450" s="3" t="inlineStr"/>
-      <c r="M450" s="3" t="inlineStr">
-        <is>
-          <t>1–12 oy 25%, 13–24 oy 26%, 25–36 oy 26.5% (rasmiy daromadli)</t>
-        </is>
-      </c>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L450" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M450" s="3" t="inlineStr"/>
       <c r="N450" s="6" t="inlineStr">
         <is>
-          <t>https://ziraatbank.uz/uz/mikroqarz</t>
+          <t>https://ziraatbank.uz/uz/iste-mol-kredit----yashil-komfort---</t>
         </is>
       </c>
     </row>
@@ -28248,24 +28264,24 @@
       </c>
       <c r="C451" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>Iste'mol</t>
         </is>
       </c>
       <c r="D451" s="3" t="inlineStr">
         <is>
-          <t>Mikroqarz</t>
+          <t>ECO SARMOYA</t>
         </is>
       </c>
       <c r="E451" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F451" s="3" t="n">
         <v>25</v>
-      </c>
-      <c r="F451" s="3" t="n">
-        <v>26.5</v>
       </c>
       <c r="G451" s="3" t="inlineStr"/>
       <c r="H451" s="3" t="inlineStr">
         <is>
-          <t>1 oy – 3 yil</t>
+          <t>6 oy – 5 yil</t>
         </is>
       </c>
       <c r="I451" s="3" t="inlineStr"/>
@@ -28287,12 +28303,128 @@
       <c r="M451" s="3" t="inlineStr"/>
       <c r="N451" s="6" t="inlineStr">
         <is>
+          <t>https://ziraatbank.uz/uz/eco-sarmoya</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="3" t="inlineStr">
+        <is>
+          <t>Ziraat Bank O'zbekiston</t>
+        </is>
+      </c>
+      <c r="B452" s="3" t="inlineStr">
+        <is>
+          <t>Jismoniy</t>
+        </is>
+      </c>
+      <c r="C452" s="3" t="inlineStr">
+        <is>
+          <t>Mikroqarz</t>
+        </is>
+      </c>
+      <c r="D452" s="3" t="inlineStr">
+        <is>
+          <t>Mikroqarz</t>
+        </is>
+      </c>
+      <c r="E452" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F452" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G452" s="3" t="inlineStr"/>
+      <c r="H452" s="3" t="inlineStr">
+        <is>
+          <t>1–36 oy</t>
+        </is>
+      </c>
+      <c r="I452" s="3" t="inlineStr">
+        <is>
+          <t>20 mln dan</t>
+        </is>
+      </c>
+      <c r="J452" s="3" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="K452" s="3" t="inlineStr">
+        <is>
+          <t>Qo'lda tekshirilgan</t>
+        </is>
+      </c>
+      <c r="L452" s="3" t="inlineStr"/>
+      <c r="M452" s="3" t="inlineStr">
+        <is>
+          <t>1–12 oy 25%, 13–24 oy 26%, 25–36 oy 26.5% (rasmiy daromadli)</t>
+        </is>
+      </c>
+      <c r="N452" s="6" t="inlineStr">
+        <is>
           <t>https://ziraatbank.uz/uz/mikroqarz</t>
         </is>
       </c>
     </row>
+    <row r="453">
+      <c r="A453" s="3" t="inlineStr">
+        <is>
+          <t>Ziraat Bank O'zbekiston</t>
+        </is>
+      </c>
+      <c r="B453" s="3" t="inlineStr">
+        <is>
+          <t>Jismoniy</t>
+        </is>
+      </c>
+      <c r="C453" s="3" t="inlineStr">
+        <is>
+          <t>Mikroqarz</t>
+        </is>
+      </c>
+      <c r="D453" s="3" t="inlineStr">
+        <is>
+          <t>Mikroqarz</t>
+        </is>
+      </c>
+      <c r="E453" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F453" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G453" s="3" t="inlineStr"/>
+      <c r="H453" s="3" t="inlineStr">
+        <is>
+          <t>1 oy – 3 yil</t>
+        </is>
+      </c>
+      <c r="I453" s="3" t="inlineStr"/>
+      <c r="J453" s="3" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="K453" s="3" t="inlineStr">
+        <is>
+          <t>Saytdan avtomatik</t>
+        </is>
+      </c>
+      <c r="L453" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M453" s="3" t="inlineStr"/>
+      <c r="N453" s="6" t="inlineStr">
+        <is>
+          <t>https://ziraatbank.uz/uz/mikroqarz</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N451"/>
+  <autoFilter ref="A1:N453"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -28744,6 +28876,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N449" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N450" r:id="rId449"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N453" r:id="rId452"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29340,14 +29474,14 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>24.99 – 25.99</t>
+          <t>0 – 29.5</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
